--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -656,242 +656,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1200</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>300</v>
       </c>
       <c r="I9" s="3">
         <v>300</v>
@@ -903,31 +910,31 @@
         <v>300</v>
       </c>
       <c r="L9" s="3">
+        <v>300</v>
+      </c>
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>300</v>
       </c>
       <c r="R9" s="3">
         <v>300</v>
       </c>
       <c r="S9" s="3">
+        <v>300</v>
+      </c>
+      <c r="T9" s="3">
         <v>400</v>
-      </c>
-      <c r="T9" s="3">
-        <v>300</v>
       </c>
       <c r="U9" s="3">
         <v>300</v>
@@ -945,7 +952,7 @@
         <v>300</v>
       </c>
       <c r="Z9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AA9" s="3">
         <v>400</v>
@@ -954,105 +961,111 @@
         <v>400</v>
       </c>
       <c r="AC9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD9" s="3">
         <v>600</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>600</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1276,8 +1296,8 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1285,21 +1305,21 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1315,8 +1335,8 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1345,14 +1365,17 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>4</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1434,14 +1457,17 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1400</v>
       </c>
       <c r="V17" s="3">
         <v>1400</v>
       </c>
       <c r="W17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1800</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>4200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7600</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
         <v>0</v>
       </c>
       <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-200</v>
       </c>
       <c r="AB18" s="3">
         <v>-200</v>
       </c>
       <c r="AC18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-600</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1690,19 +1724,19 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
@@ -1711,156 +1745,162 @@
         <v>-100</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>-100</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-300</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
-      </c>
       <c r="AB21" s="3">
         <v>0</v>
       </c>
       <c r="AC21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1931,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>100</v>
@@ -1942,192 +1982,201 @@
       <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>4</v>
+      <c r="AD22" s="3">
+        <v>100</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-300</v>
       </c>
       <c r="AB23" s="3">
         <v>-300</v>
       </c>
       <c r="AC23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-700</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>-200</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-100</v>
       </c>
       <c r="Y24" s="3">
         <v>-100</v>
       </c>
       <c r="Z24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-100</v>
       </c>
       <c r="AB24" s="3">
         <v>-100</v>
       </c>
       <c r="AC24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-100</v>
       </c>
       <c r="U26" s="3">
         <v>-100</v>
       </c>
       <c r="V26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-200</v>
       </c>
       <c r="AB26" s="3">
         <v>-200</v>
       </c>
       <c r="AC26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-100</v>
       </c>
       <c r="U27" s="3">
         <v>-100</v>
       </c>
       <c r="V27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-200</v>
       </c>
       <c r="AB27" s="3">
         <v>-200</v>
       </c>
       <c r="AC27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2514,14 +2575,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>4</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2533,17 +2594,17 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>100</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>300</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -2554,25 +2615,28 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>4</v>
+      <c r="AC29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2758,19 +2828,19 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
@@ -2779,156 +2849,162 @@
         <v>100</v>
       </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-200</v>
       </c>
       <c r="AB33" s="3">
         <v>-200</v>
       </c>
       <c r="AC33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-200</v>
       </c>
       <c r="AB35" s="3">
         <v>-200</v>
       </c>
       <c r="AC35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E41" s="3">
         <v>8500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2400</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3437,14 +3527,17 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>4</v>
+      <c r="AD42" s="3">
+        <v>0</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3458,16 +3551,16 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -3485,11 +3578,11 @@
         <v>100</v>
       </c>
       <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -3497,43 +3590,46 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
       <c r="X43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
         <v>200</v>
       </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
         <v>100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>300</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3615,28 +3711,31 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>4</v>
+      <c r="AD44" s="3">
+        <v>0</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E45" s="3">
         <v>600</v>
       </c>
       <c r="F45" s="3">
+        <v>600</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
       </c>
       <c r="H45" s="3">
         <v>500</v>
@@ -3645,37 +3744,37 @@
         <v>500</v>
       </c>
       <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>300</v>
       </c>
       <c r="R45" s="3">
         <v>300</v>
       </c>
       <c r="S45" s="3">
+        <v>300</v>
+      </c>
+      <c r="T45" s="3">
         <v>500</v>
-      </c>
-      <c r="T45" s="3">
-        <v>300</v>
       </c>
       <c r="U45" s="3">
         <v>300</v>
@@ -3684,34 +3783,37 @@
         <v>300</v>
       </c>
       <c r="W45" s="3">
+        <v>300</v>
+      </c>
+      <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>300</v>
       </c>
       <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
+      <c r="AD45" s="3">
+        <v>300</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3793,49 +3895,52 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
+      <c r="AD46" s="3">
+        <v>0</v>
       </c>
       <c r="AE46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2200</v>
       </c>
       <c r="I47" s="3">
         <v>2200</v>
       </c>
       <c r="J47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K47" s="3">
         <v>900</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1000</v>
       </c>
       <c r="L47" s="3">
         <v>1000</v>
       </c>
       <c r="M47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N47" s="3">
         <v>1200</v>
-      </c>
-      <c r="N47" s="3">
-        <v>1300</v>
       </c>
       <c r="O47" s="3">
         <v>1300</v>
@@ -3847,7 +3952,7 @@
         <v>1300</v>
       </c>
       <c r="R47" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="S47" s="3">
         <v>2400</v>
@@ -3856,7 +3961,7 @@
         <v>2400</v>
       </c>
       <c r="U47" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="V47" s="3">
         <v>2600</v>
@@ -3865,36 +3970,39 @@
         <v>2600</v>
       </c>
       <c r="X47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y47" s="3">
         <v>3800</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>4000</v>
       </c>
       <c r="Z47" s="3">
         <v>4000</v>
       </c>
       <c r="AA47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AB47" s="3">
         <v>4400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5500</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="E48" s="3">
         <v>10700</v>
@@ -3903,37 +4011,37 @@
         <v>10700</v>
       </c>
       <c r="G48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="H48" s="3">
         <v>10500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>10500</v>
       </c>
       <c r="K48" s="3">
         <v>10500</v>
       </c>
       <c r="L48" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="M48" s="3">
         <v>10600</v>
       </c>
       <c r="N48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="O48" s="3">
         <v>10500</v>
-      </c>
-      <c r="O48" s="3">
-        <v>10600</v>
       </c>
       <c r="P48" s="3">
         <v>10600</v>
       </c>
       <c r="Q48" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="R48" s="3">
         <v>10700</v>
@@ -3942,7 +4050,7 @@
         <v>10700</v>
       </c>
       <c r="T48" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="U48" s="3">
         <v>10900</v>
@@ -3951,34 +4059,37 @@
         <v>10900</v>
       </c>
       <c r="W48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="X48" s="3">
         <v>20400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>21100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>21300</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4060,14 +4171,17 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>4</v>
+      <c r="AD49" s="3">
+        <v>0</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,32 +4361,35 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
@@ -4283,58 +4403,61 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>1400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1700</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1600</v>
       </c>
       <c r="U52" s="3">
         <v>1600</v>
       </c>
       <c r="V52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W52" s="3">
         <v>10400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5800</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1000</v>
       </c>
       <c r="AA52" s="3">
         <v>1000</v>
       </c>
       <c r="AB52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E54" s="3">
         <v>24400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21400</v>
-      </c>
-      <c r="I54" s="3">
-        <v>21600</v>
       </c>
       <c r="J54" s="3">
         <v>21600</v>
       </c>
       <c r="K54" s="3">
+        <v>21600</v>
+      </c>
+      <c r="L54" s="3">
         <v>22500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28100</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>28300</v>
       </c>
       <c r="Z54" s="3">
         <v>28300</v>
       </c>
       <c r="AA54" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AB54" s="3">
         <v>30000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30900</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,19 +4707,20 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>500</v>
       </c>
       <c r="F57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>400</v>
@@ -4601,22 +4732,22 @@
         <v>400</v>
       </c>
       <c r="J57" s="3">
+        <v>400</v>
+      </c>
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>400</v>
       </c>
       <c r="M57" s="3">
         <v>400</v>
       </c>
       <c r="N57" s="3">
+        <v>400</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>300</v>
@@ -4625,49 +4756,52 @@
         <v>300</v>
       </c>
       <c r="R57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
       </c>
       <c r="T57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
       </c>
       <c r="V57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W57" s="3">
         <v>200</v>
       </c>
       <c r="X57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y57" s="3">
         <v>300</v>
       </c>
       <c r="Z57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA57" s="3">
         <v>200</v>
       </c>
       <c r="AB57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
+      <c r="AD57" s="3">
+        <v>300</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4680,8 +4814,8 @@
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4702,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>500</v>
@@ -4711,7 +4845,7 @@
         <v>500</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4729,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>300</v>
       </c>
       <c r="Y58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z58" s="3">
         <v>200</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>300</v>
       </c>
       <c r="AA58" s="3">
         <v>300</v>
@@ -4749,19 +4883,22 @@
       <c r="AC58" s="3">
         <v>300</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>4</v>
+      <c r="AD58" s="3">
+        <v>300</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
         <v>300</v>
@@ -4770,82 +4907,85 @@
         <v>300</v>
       </c>
       <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>300</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
       </c>
       <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
         <v>500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>300</v>
       </c>
       <c r="Q59" s="3">
         <v>300</v>
       </c>
       <c r="R59" s="3">
+        <v>300</v>
+      </c>
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4800</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4927,14 +5067,17 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
+      <c r="AD60" s="3">
+        <v>0</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4987,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>100</v>
@@ -4996,106 +5139,109 @@
         <v>100</v>
       </c>
       <c r="W61" s="3">
+        <v>100</v>
+      </c>
+      <c r="X61" s="3">
         <v>6000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6400</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>6500</v>
       </c>
       <c r="AC61" s="3">
         <v>6500</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
       </c>
       <c r="I62" s="3">
         <v>400</v>
       </c>
       <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1800</v>
-      </c>
-      <c r="R62" s="3">
-        <v>1700</v>
       </c>
       <c r="S62" s="3">
         <v>1700</v>
       </c>
       <c r="T62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U62" s="3">
         <v>2700</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>6200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z62" s="3">
         <v>3100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2700</v>
-      </c>
-      <c r="M66" s="3">
-        <v>3400</v>
       </c>
       <c r="N66" s="3">
         <v>3400</v>
       </c>
       <c r="O66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P66" s="3">
         <v>2900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>12300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12400</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5761,14 +5929,17 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-      <c r="AD70" s="3" t="s">
-        <v>4</v>
+      <c r="AD70" s="3">
+        <v>0</v>
       </c>
       <c r="AE70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E72" s="3">
         <v>4600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2100</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-1900</v>
       </c>
       <c r="Q72" s="3">
         <v>-1900</v>
       </c>
       <c r="R72" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="S72" s="3">
         <v>-1100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1900</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E76" s="3">
         <v>22100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15000</v>
-      </c>
-      <c r="P76" s="3">
-        <v>14600</v>
       </c>
       <c r="Q76" s="3">
         <v>14600</v>
       </c>
       <c r="R76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="S76" s="3">
         <v>15400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>18500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18500</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-200</v>
       </c>
       <c r="AB81" s="3">
         <v>-200</v>
       </c>
       <c r="AC81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6666,7 +6865,7 @@
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -6689,14 +6888,17 @@
       <c r="AC83" s="3">
         <v>200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
+      <c r="AD83" s="3">
+        <v>200</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7149,88 +7366,91 @@
         <v>-300</v>
       </c>
       <c r="E89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F89" s="3">
         <v>4600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="W89" s="3">
         <v>-400</v>
       </c>
       <c r="X89" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="Y89" s="3">
         <v>-100</v>
       </c>
       <c r="Z89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
+      <c r="AD89" s="3">
+        <v>0</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,64 +7482,65 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-200</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7328,11 +7549,11 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -7343,16 +7564,19 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,44 +7756,47 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -7574,52 +7804,55 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>900</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>1100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>600</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8040,20 +8286,20 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -8061,13 +8307,13 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W100" s="3">
         <v>-100</v>
@@ -8088,16 +8334,19 @@
         <v>-100</v>
       </c>
       <c r="AC100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8179,99 +8428,105 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>700</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -656,232 +656,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1200</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -889,19 +896,19 @@
         <v>400</v>
       </c>
       <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>300</v>
       </c>
       <c r="J9" s="3">
         <v>300</v>
@@ -913,31 +920,31 @@
         <v>300</v>
       </c>
       <c r="M9" s="3">
+        <v>300</v>
+      </c>
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
-      </c>
-      <c r="R9" s="3">
-        <v>300</v>
       </c>
       <c r="S9" s="3">
         <v>300</v>
       </c>
       <c r="T9" s="3">
+        <v>300</v>
+      </c>
+      <c r="U9" s="3">
         <v>400</v>
-      </c>
-      <c r="U9" s="3">
-        <v>300</v>
       </c>
       <c r="V9" s="3">
         <v>300</v>
@@ -955,7 +962,7 @@
         <v>300</v>
       </c>
       <c r="AA9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AB9" s="3">
         <v>400</v>
@@ -964,108 +971,114 @@
         <v>400</v>
       </c>
       <c r="AD9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE9" s="3">
         <v>600</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>600</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1299,8 +1319,8 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1308,21 +1328,21 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1338,8 +1358,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1368,14 +1388,17 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>4</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1460,14 +1483,17 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1400</v>
       </c>
       <c r="W17" s="3">
         <v>1400</v>
       </c>
       <c r="X17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1800</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>4200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7600</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-200</v>
       </c>
       <c r="AC18" s="3">
         <v>-200</v>
       </c>
       <c r="AD18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-600</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,31 +1748,32 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1748,159 +1782,165 @@
         <v>-100</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>-100</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-300</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
-        <v>0</v>
-      </c>
       <c r="AC21" s="3">
         <v>0</v>
       </c>
       <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1974,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
@@ -1985,14 +2025,17 @@
       <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>4</v>
+      <c r="AE22" s="3">
+        <v>100</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2000,91 +2043,94 @@
         <v>-400</v>
       </c>
       <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-300</v>
       </c>
       <c r="AC23" s="3">
         <v>-300</v>
       </c>
       <c r="AD23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-700</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2092,91 +2138,94 @@
         <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>-200</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>-100</v>
       </c>
       <c r="Z24" s="3">
         <v>-100</v>
       </c>
       <c r="AA24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>-100</v>
       </c>
       <c r="AC24" s="3">
         <v>-100</v>
       </c>
       <c r="AD24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2316,11 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2276,91 +2328,94 @@
         <v>-300</v>
       </c>
       <c r="E26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-100</v>
       </c>
       <c r="V26" s="3">
         <v>-100</v>
       </c>
       <c r="W26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-200</v>
       </c>
       <c r="AC26" s="3">
         <v>-200</v>
       </c>
       <c r="AD26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2368,91 +2423,94 @@
         <v>-300</v>
       </c>
       <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-100</v>
       </c>
       <c r="V27" s="3">
         <v>-100</v>
       </c>
       <c r="W27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-200</v>
       </c>
       <c r="AC27" s="3">
         <v>-200</v>
       </c>
       <c r="AD27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2578,14 +2639,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>4</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2597,17 +2658,17 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>100</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>300</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2618,25 +2679,28 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-200</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>4</v>
+      <c r="AD29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,31 +2886,34 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -2852,67 +2922,70 @@
         <v>100</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>100</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2920,91 +2993,94 @@
         <v>-300</v>
       </c>
       <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-200</v>
       </c>
       <c r="AC33" s="3">
         <v>-200</v>
       </c>
       <c r="AD33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3171,11 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3104,188 +3183,194 @@
         <v>-300</v>
       </c>
       <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-200</v>
       </c>
       <c r="AC35" s="3">
         <v>-200</v>
       </c>
       <c r="AD35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E41" s="3">
         <v>9300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2400</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3530,19 +3620,22 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>4</v>
+      <c r="AE42" s="3">
+        <v>0</v>
       </c>
       <c r="AF42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -3554,16 +3647,16 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
@@ -3581,11 +3674,11 @@
         <v>100</v>
       </c>
       <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3">
         <v>600</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
@@ -3593,43 +3686,46 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3">
         <v>200</v>
       </c>
       <c r="AA43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
       <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>300</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3714,31 +3810,34 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>4</v>
+      <c r="AE44" s="3">
+        <v>0</v>
       </c>
       <c r="AF44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>600</v>
       </c>
       <c r="F45" s="3">
         <v>600</v>
       </c>
       <c r="G45" s="3">
+        <v>600</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>500</v>
       </c>
       <c r="I45" s="3">
         <v>500</v>
@@ -3747,37 +3846,37 @@
         <v>500</v>
       </c>
       <c r="K45" s="3">
+        <v>500</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
-      </c>
-      <c r="R45" s="3">
-        <v>300</v>
       </c>
       <c r="S45" s="3">
         <v>300</v>
       </c>
       <c r="T45" s="3">
+        <v>300</v>
+      </c>
+      <c r="U45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>300</v>
       </c>
       <c r="V45" s="3">
         <v>300</v>
@@ -3786,34 +3885,37 @@
         <v>300</v>
       </c>
       <c r="X45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y45" s="3">
         <v>500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>400</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>300</v>
       </c>
       <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
+      <c r="AE45" s="3">
+        <v>300</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3898,52 +4000,55 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
+      <c r="AE46" s="3">
+        <v>0</v>
       </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E47" s="3">
         <v>3000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2200</v>
       </c>
       <c r="J47" s="3">
         <v>2200</v>
       </c>
       <c r="K47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L47" s="3">
         <v>900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1000</v>
       </c>
       <c r="M47" s="3">
         <v>1000</v>
       </c>
       <c r="N47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O47" s="3">
         <v>1200</v>
-      </c>
-      <c r="O47" s="3">
-        <v>1300</v>
       </c>
       <c r="P47" s="3">
         <v>1300</v>
@@ -3955,7 +4060,7 @@
         <v>1300</v>
       </c>
       <c r="S47" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="T47" s="3">
         <v>2400</v>
@@ -3964,7 +4069,7 @@
         <v>2400</v>
       </c>
       <c r="V47" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="W47" s="3">
         <v>2600</v>
@@ -3973,39 +4078,42 @@
         <v>2600</v>
       </c>
       <c r="Y47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Z47" s="3">
         <v>3800</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>4000</v>
       </c>
       <c r="AA47" s="3">
         <v>4000</v>
       </c>
       <c r="AB47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AC47" s="3">
         <v>4400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5500</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E48" s="3">
         <v>10800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>10700</v>
       </c>
       <c r="F48" s="3">
         <v>10700</v>
@@ -4014,37 +4122,37 @@
         <v>10700</v>
       </c>
       <c r="H48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I48" s="3">
         <v>10500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>10500</v>
       </c>
       <c r="L48" s="3">
         <v>10500</v>
       </c>
       <c r="M48" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="N48" s="3">
         <v>10600</v>
       </c>
       <c r="O48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="P48" s="3">
         <v>10500</v>
-      </c>
-      <c r="P48" s="3">
-        <v>10600</v>
       </c>
       <c r="Q48" s="3">
         <v>10600</v>
       </c>
       <c r="R48" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="S48" s="3">
         <v>10700</v>
@@ -4053,7 +4161,7 @@
         <v>10700</v>
       </c>
       <c r="U48" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="V48" s="3">
         <v>10900</v>
@@ -4062,34 +4170,37 @@
         <v>10900</v>
       </c>
       <c r="X48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Y48" s="3">
         <v>20400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>21100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>21300</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4174,14 +4285,17 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>4</v>
+      <c r="AE49" s="3">
+        <v>0</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,35 +4481,38 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4406,58 +4526,61 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1700</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1600</v>
       </c>
       <c r="V52" s="3">
         <v>1600</v>
       </c>
       <c r="W52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X52" s="3">
         <v>10400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5800</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>1000</v>
       </c>
       <c r="AB52" s="3">
         <v>1000</v>
       </c>
       <c r="AC52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1100</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E54" s="3">
         <v>23700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>24700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21400</v>
-      </c>
-      <c r="J54" s="3">
-        <v>21600</v>
       </c>
       <c r="K54" s="3">
         <v>21600</v>
       </c>
       <c r="L54" s="3">
+        <v>21600</v>
+      </c>
+      <c r="M54" s="3">
         <v>22500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>27000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28100</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>28300</v>
       </c>
       <c r="AA54" s="3">
         <v>28300</v>
       </c>
       <c r="AB54" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AC54" s="3">
         <v>30000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30900</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,22 +4838,23 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>500</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
       </c>
       <c r="G57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H57" s="3">
         <v>400</v>
@@ -4735,22 +4866,22 @@
         <v>400</v>
       </c>
       <c r="K57" s="3">
+        <v>400</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>400</v>
       </c>
       <c r="N57" s="3">
         <v>400</v>
       </c>
       <c r="O57" s="3">
+        <v>400</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>300</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
@@ -4759,49 +4890,52 @@
         <v>300</v>
       </c>
       <c r="S57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
       <c r="U57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
       </c>
       <c r="W57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X57" s="3">
         <v>200</v>
       </c>
       <c r="Y57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z57" s="3">
         <v>300</v>
       </c>
       <c r="AA57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB57" s="3">
         <v>200</v>
       </c>
       <c r="AC57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD57" s="3">
         <v>300</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
+      <c r="AE57" s="3">
+        <v>300</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4817,8 +4951,8 @@
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -4839,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>500</v>
@@ -4848,7 +4982,7 @@
         <v>500</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4866,16 +5000,16 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
         <v>300</v>
       </c>
       <c r="Z58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA58" s="3">
         <v>200</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>300</v>
       </c>
       <c r="AB58" s="3">
         <v>300</v>
@@ -4886,22 +5020,25 @@
       <c r="AD58" s="3">
         <v>300</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>4</v>
+      <c r="AE58" s="3">
+        <v>300</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
         <v>700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>300</v>
@@ -4910,82 +5047,85 @@
         <v>300</v>
       </c>
       <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>300</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>300</v>
       </c>
       <c r="R59" s="3">
         <v>300</v>
       </c>
       <c r="S59" s="3">
+        <v>300</v>
+      </c>
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4800</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5070,14 +5210,17 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
+      <c r="AE60" s="3">
+        <v>0</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5133,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>100</v>
@@ -5142,34 +5285,37 @@
         <v>100</v>
       </c>
       <c r="X61" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y61" s="3">
         <v>6000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6400</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>6500</v>
       </c>
       <c r="AD61" s="3">
         <v>6500</v>
       </c>
       <c r="AE61" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5177,74 +5323,74 @@
         <v>600</v>
       </c>
       <c r="E62" s="3">
+        <v>600</v>
+      </c>
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
       </c>
       <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1800</v>
-      </c>
-      <c r="S62" s="3">
-        <v>1700</v>
       </c>
       <c r="T62" s="3">
         <v>1700</v>
       </c>
       <c r="U62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V62" s="3">
         <v>2700</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
       <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
         <v>6200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA62" s="3">
         <v>3100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2700</v>
-      </c>
-      <c r="N66" s="3">
-        <v>3400</v>
       </c>
       <c r="O66" s="3">
         <v>3400</v>
       </c>
       <c r="P66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12400</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5932,14 +6100,17 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-      <c r="AE70" s="3" t="s">
-        <v>4</v>
+      <c r="AE70" s="3">
+        <v>0</v>
       </c>
       <c r="AF70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2100</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-1900</v>
       </c>
       <c r="R72" s="3">
         <v>-1900</v>
       </c>
       <c r="S72" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="T72" s="3">
         <v>-1100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1900</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E76" s="3">
         <v>21900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15000</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>14600</v>
       </c>
       <c r="R76" s="3">
         <v>14600</v>
       </c>
       <c r="S76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="T76" s="3">
         <v>15400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18500</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6771,111 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6688,91 +6883,94 @@
         <v>-300</v>
       </c>
       <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-200</v>
       </c>
       <c r="AC81" s="3">
         <v>-200</v>
       </c>
       <c r="AD81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6868,7 +7067,7 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -6891,14 +7090,17 @@
       <c r="AD83" s="3">
         <v>200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
+      <c r="AE83" s="3">
+        <v>200</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
         <v>-300</v>
       </c>
       <c r="F89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G89" s="3">
         <v>4600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>400</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="X89" s="3">
         <v>-400</v>
       </c>
       <c r="Y89" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="Z89" s="3">
         <v>-100</v>
       </c>
       <c r="AA89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
+      <c r="AE89" s="3">
+        <v>0</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,67 +7703,68 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7552,11 +7773,11 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
@@ -7567,16 +7788,19 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,47 +7986,50 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>400</v>
+      </c>
+      <c r="E94" s="3">
         <v>1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -7807,52 +8037,55 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>900</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>1100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>600</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8496,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8289,20 +8535,20 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -8310,13 +8556,13 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X100" s="3">
         <v>-100</v>
@@ -8337,16 +8583,19 @@
         <v>-100</v>
       </c>
       <c r="AD100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8431,102 +8680,108 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>700</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -656,144 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -801,117 +804,120 @@
         <v>1000</v>
       </c>
       <c r="E8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="3">
         <v>2000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1200</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
         <v>400</v>
       </c>
       <c r="F9" s="3">
+        <v>400</v>
+      </c>
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>300</v>
       </c>
       <c r="K9" s="3">
         <v>300</v>
@@ -923,31 +929,31 @@
         <v>300</v>
       </c>
       <c r="N9" s="3">
+        <v>300</v>
+      </c>
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
-      </c>
-      <c r="S9" s="3">
-        <v>300</v>
       </c>
       <c r="T9" s="3">
         <v>300</v>
       </c>
       <c r="U9" s="3">
+        <v>300</v>
+      </c>
+      <c r="V9" s="3">
         <v>400</v>
-      </c>
-      <c r="V9" s="3">
-        <v>300</v>
       </c>
       <c r="W9" s="3">
         <v>300</v>
@@ -965,7 +971,7 @@
         <v>300</v>
       </c>
       <c r="AB9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AC9" s="3">
         <v>400</v>
@@ -974,111 +980,117 @@
         <v>400</v>
       </c>
       <c r="AE9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF9" s="3">
         <v>600</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>600</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1322,8 +1341,8 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1331,21 +1350,21 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1361,8 +1380,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1391,14 +1410,17 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>4</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1486,14 +1508,17 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1400</v>
       </c>
       <c r="X17" s="3">
         <v>1400</v>
       </c>
       <c r="Y17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1800</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>4200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7600</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-200</v>
       </c>
       <c r="AD18" s="3">
         <v>-200</v>
       </c>
       <c r="AE18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-600</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,34 +1781,35 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>-100</v>
@@ -1785,162 +1818,168 @@
         <v>-100</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>-100</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>-900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3">
-        <v>0</v>
-      </c>
       <c r="AD21" s="3">
         <v>0</v>
       </c>
       <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-400</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2017,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
@@ -2028,204 +2067,213 @@
       <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>4</v>
+      <c r="AF22" s="3">
+        <v>100</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-400</v>
+        <v>-700</v>
       </c>
       <c r="E23" s="3">
         <v>-400</v>
       </c>
       <c r="F23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-300</v>
       </c>
       <c r="AD23" s="3">
         <v>-300</v>
       </c>
       <c r="AE23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-700</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>-200</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-100</v>
       </c>
       <c r="AA24" s="3">
         <v>-100</v>
       </c>
       <c r="AB24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>-100</v>
       </c>
       <c r="AD24" s="3">
         <v>-100</v>
       </c>
       <c r="AE24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E26" s="3">
         <v>-300</v>
       </c>
       <c r="F26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-100</v>
       </c>
       <c r="W26" s="3">
         <v>-100</v>
       </c>
       <c r="X26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-200</v>
       </c>
       <c r="AD26" s="3">
         <v>-200</v>
       </c>
       <c r="AE26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E27" s="3">
         <v>-300</v>
       </c>
       <c r="F27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-100</v>
       </c>
       <c r="W27" s="3">
         <v>-100</v>
       </c>
       <c r="X27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-200</v>
       </c>
       <c r="AD27" s="3">
         <v>-200</v>
       </c>
       <c r="AE27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2642,14 +2702,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>4</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2661,17 +2721,17 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>100</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>300</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
@@ -2682,25 +2742,28 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>4</v>
+      <c r="AE29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,34 +2955,37 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>100</v>
@@ -2925,162 +2994,168 @@
         <v>100</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>100</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E33" s="3">
         <v>-300</v>
       </c>
       <c r="F33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-200</v>
       </c>
       <c r="AD33" s="3">
         <v>-200</v>
       </c>
       <c r="AE33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E35" s="3">
         <v>-300</v>
       </c>
       <c r="F35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-200</v>
       </c>
       <c r="AD35" s="3">
         <v>-200</v>
       </c>
       <c r="AE35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E41" s="3">
         <v>9500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2400</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3623,22 +3712,25 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>4</v>
+      <c r="AF42" s="3">
+        <v>0</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
-      </c>
-      <c r="E43" s="3">
-        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -3650,16 +3742,16 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -3677,11 +3769,11 @@
         <v>100</v>
       </c>
       <c r="R43" s="3">
+        <v>100</v>
+      </c>
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
@@ -3689,43 +3781,46 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>500</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
       <c r="Z43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3">
         <v>200</v>
       </c>
       <c r="AB43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
       <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
         <v>100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>300</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3813,34 +3908,37 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>4</v>
+      <c r="AF44" s="3">
+        <v>0</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>600</v>
       </c>
       <c r="G45" s="3">
         <v>600</v>
       </c>
       <c r="H45" s="3">
+        <v>600</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>500</v>
       </c>
       <c r="J45" s="3">
         <v>500</v>
@@ -3849,37 +3947,37 @@
         <v>500</v>
       </c>
       <c r="L45" s="3">
+        <v>500</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
-      </c>
-      <c r="S45" s="3">
-        <v>300</v>
       </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
       <c r="U45" s="3">
+        <v>300</v>
+      </c>
+      <c r="V45" s="3">
         <v>500</v>
-      </c>
-      <c r="V45" s="3">
-        <v>300</v>
       </c>
       <c r="W45" s="3">
         <v>300</v>
@@ -3888,34 +3986,37 @@
         <v>300</v>
       </c>
       <c r="Y45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>400</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>300</v>
       </c>
       <c r="AE45" s="3">
         <v>300</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>4</v>
+      <c r="AF45" s="3">
+        <v>300</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4003,55 +4104,58 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>4</v>
+      <c r="AF46" s="3">
+        <v>0</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3700</v>
-      </c>
-      <c r="J47" s="3">
-        <v>2200</v>
       </c>
       <c r="K47" s="3">
         <v>2200</v>
       </c>
       <c r="L47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M47" s="3">
         <v>900</v>
-      </c>
-      <c r="M47" s="3">
-        <v>1000</v>
       </c>
       <c r="N47" s="3">
         <v>1000</v>
       </c>
       <c r="O47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P47" s="3">
         <v>1200</v>
-      </c>
-      <c r="P47" s="3">
-        <v>1300</v>
       </c>
       <c r="Q47" s="3">
         <v>1300</v>
@@ -4063,7 +4167,7 @@
         <v>1300</v>
       </c>
       <c r="T47" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="U47" s="3">
         <v>2400</v>
@@ -4072,7 +4176,7 @@
         <v>2400</v>
       </c>
       <c r="W47" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="X47" s="3">
         <v>2600</v>
@@ -4081,42 +4185,45 @@
         <v>2600</v>
       </c>
       <c r="Z47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AA47" s="3">
         <v>3800</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>4000</v>
       </c>
       <c r="AB47" s="3">
         <v>4000</v>
       </c>
       <c r="AC47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AD47" s="3">
         <v>4400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5500</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E48" s="3">
         <v>10500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>10700</v>
       </c>
       <c r="G48" s="3">
         <v>10700</v>
@@ -4125,37 +4232,37 @@
         <v>10700</v>
       </c>
       <c r="I48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J48" s="3">
         <v>10500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>10500</v>
       </c>
       <c r="M48" s="3">
         <v>10500</v>
       </c>
       <c r="N48" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="O48" s="3">
         <v>10600</v>
       </c>
       <c r="P48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="Q48" s="3">
         <v>10500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>10600</v>
       </c>
       <c r="R48" s="3">
         <v>10600</v>
       </c>
       <c r="S48" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="T48" s="3">
         <v>10700</v>
@@ -4164,7 +4271,7 @@
         <v>10700</v>
       </c>
       <c r="V48" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="W48" s="3">
         <v>10900</v>
@@ -4173,34 +4280,37 @@
         <v>10900</v>
       </c>
       <c r="Y48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Z48" s="3">
         <v>20400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>21100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>21300</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4288,14 +4398,17 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>4</v>
+      <c r="AF49" s="3">
+        <v>0</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,38 +4600,41 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -4529,58 +4648,61 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>1400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1700</v>
-      </c>
-      <c r="V52" s="3">
-        <v>1600</v>
       </c>
       <c r="W52" s="3">
         <v>1600</v>
       </c>
       <c r="X52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y52" s="3">
         <v>10400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5800</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>1000</v>
       </c>
       <c r="AC52" s="3">
         <v>1000</v>
       </c>
       <c r="AD52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE52" s="3">
         <v>1200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1100</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E54" s="3">
         <v>23300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>24400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21400</v>
-      </c>
-      <c r="K54" s="3">
-        <v>21600</v>
       </c>
       <c r="L54" s="3">
         <v>21600</v>
       </c>
       <c r="M54" s="3">
+        <v>21600</v>
+      </c>
+      <c r="N54" s="3">
         <v>22500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>27000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28100</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>28300</v>
       </c>
       <c r="AB54" s="3">
         <v>28300</v>
       </c>
       <c r="AC54" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AD54" s="3">
         <v>30000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30900</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,25 +4968,26 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>500</v>
       </c>
       <c r="H57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I57" s="3">
         <v>400</v>
@@ -4869,22 +4999,22 @@
         <v>400</v>
       </c>
       <c r="L57" s="3">
+        <v>400</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>400</v>
       </c>
       <c r="O57" s="3">
         <v>400</v>
       </c>
       <c r="P57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>300</v>
       </c>
       <c r="R57" s="3">
         <v>300</v>
@@ -4893,49 +5023,52 @@
         <v>300</v>
       </c>
       <c r="T57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U57" s="3">
         <v>200</v>
       </c>
       <c r="V57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W57" s="3">
         <v>300</v>
       </c>
       <c r="X57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y57" s="3">
         <v>200</v>
       </c>
       <c r="Z57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA57" s="3">
         <v>300</v>
       </c>
       <c r="AB57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
       </c>
       <c r="AD57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
+      <c r="AF57" s="3">
+        <v>300</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4954,8 +5087,8 @@
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4976,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>500</v>
@@ -4985,7 +5118,7 @@
         <v>500</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5003,16 +5136,16 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>300</v>
       </c>
       <c r="AA58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB58" s="3">
         <v>200</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>300</v>
       </c>
       <c r="AC58" s="3">
         <v>300</v>
@@ -5023,14 +5156,17 @@
       <c r="AE58" s="3">
         <v>300</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>4</v>
+      <c r="AF58" s="3">
+        <v>300</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5038,10 +5174,10 @@
         <v>400</v>
       </c>
       <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
         <v>700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>300</v>
       </c>
       <c r="G59" s="3">
         <v>300</v>
@@ -5050,82 +5186,85 @@
         <v>300</v>
       </c>
       <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>300</v>
       </c>
       <c r="P59" s="3">
         <v>300</v>
       </c>
       <c r="Q59" s="3">
+        <v>300</v>
+      </c>
+      <c r="R59" s="3">
         <v>500</v>
-      </c>
-      <c r="R59" s="3">
-        <v>300</v>
       </c>
       <c r="S59" s="3">
         <v>300</v>
       </c>
       <c r="T59" s="3">
+        <v>300</v>
+      </c>
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4800</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5213,14 +5352,17 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>4</v>
+      <c r="AF60" s="3">
+        <v>0</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5279,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>100</v>
@@ -5288,112 +5430,115 @@
         <v>100</v>
       </c>
       <c r="Y61" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z61" s="3">
         <v>6000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6400</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>6500</v>
       </c>
       <c r="AE61" s="3">
         <v>6500</v>
       </c>
       <c r="AF61" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
         <v>600</v>
       </c>
       <c r="F62" s="3">
+        <v>600</v>
+      </c>
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>400</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
       </c>
       <c r="L62" s="3">
+        <v>400</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1800</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1700</v>
       </c>
       <c r="U62" s="3">
         <v>1700</v>
       </c>
       <c r="V62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>6200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3">
         <v>3100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2700</v>
-      </c>
-      <c r="O66" s="3">
-        <v>3400</v>
       </c>
       <c r="P66" s="3">
         <v>3400</v>
       </c>
       <c r="Q66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R66" s="3">
         <v>2900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12400</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6103,14 +6270,17 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-      <c r="AF70" s="3" t="s">
-        <v>4</v>
+      <c r="AF70" s="3">
+        <v>0</v>
       </c>
       <c r="AG70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E72" s="3">
         <v>4000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2100</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-1900</v>
       </c>
       <c r="S72" s="3">
         <v>-1900</v>
       </c>
       <c r="T72" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U72" s="3">
         <v>-1100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1900</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E76" s="3">
         <v>21600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15000</v>
-      </c>
-      <c r="R76" s="3">
-        <v>14600</v>
       </c>
       <c r="S76" s="3">
         <v>14600</v>
       </c>
       <c r="T76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="U76" s="3">
         <v>15400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18500</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E81" s="3">
         <v>-300</v>
       </c>
       <c r="F81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-200</v>
       </c>
       <c r="AD81" s="3">
         <v>-200</v>
       </c>
       <c r="AE81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7070,7 +7268,7 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -7093,14 +7291,17 @@
       <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
+      <c r="AF83" s="3">
+        <v>200</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-300</v>
       </c>
       <c r="F89" s="3">
         <v>-300</v>
       </c>
       <c r="G89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H89" s="3">
         <v>4600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>400</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="3">
         <v>-400</v>
       </c>
       <c r="Z89" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="AA89" s="3">
         <v>-100</v>
       </c>
       <c r="AB89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
+      <c r="AF89" s="3">
+        <v>0</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,70 +7923,71 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -7776,11 +7996,11 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -7791,16 +8011,19 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,50 +8215,53 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -8040,52 +8269,55 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>900</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>3200</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>1100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>600</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8538,20 +8783,20 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -8559,13 +8804,13 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
         <v>-100</v>
@@ -8586,16 +8831,19 @@
         <v>-100</v>
       </c>
       <c r="AE100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8683,105 +8931,111 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>4</v>
+      <c r="AF101" s="3">
+        <v>0</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -656,271 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1000</v>
+        <v>2600</v>
       </c>
       <c r="E8" s="3">
         <v>1000</v>
       </c>
       <c r="F8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="3">
         <v>2000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1200</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="E9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>300</v>
-      </c>
-      <c r="H9" s="3">
-        <v>500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>300</v>
@@ -932,31 +939,31 @@
         <v>300</v>
       </c>
       <c r="O9" s="3">
+        <v>300</v>
+      </c>
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
-      </c>
-      <c r="T9" s="3">
-        <v>300</v>
       </c>
       <c r="U9" s="3">
         <v>300</v>
       </c>
       <c r="V9" s="3">
+        <v>300</v>
+      </c>
+      <c r="W9" s="3">
         <v>400</v>
-      </c>
-      <c r="W9" s="3">
-        <v>300</v>
       </c>
       <c r="X9" s="3">
         <v>300</v>
@@ -974,7 +981,7 @@
         <v>300</v>
       </c>
       <c r="AC9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AD9" s="3">
         <v>400</v>
@@ -983,114 +990,120 @@
         <v>400</v>
       </c>
       <c r="AF9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG9" s="3">
         <v>600</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>600</v>
+      </c>
+      <c r="N10" s="3">
+        <v>400</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>600</v>
+      </c>
+      <c r="R10" s="3">
+        <v>8600</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U10" s="3">
+        <v>300</v>
+      </c>
+      <c r="V10" s="3">
+        <v>400</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="Z10" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>5400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>500</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="AD10" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AF10" s="3">
         <v>1500</v>
       </c>
-      <c r="K10" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="AG10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3">
-        <v>400</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="P10" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>8600</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="T10" s="3">
-        <v>300</v>
-      </c>
-      <c r="U10" s="3">
-        <v>400</v>
-      </c>
-      <c r="V10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1500</v>
-      </c>
-      <c r="X10" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>600</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>600</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,31 +1338,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1353,21 +1373,21 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1383,8 +1403,8 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1413,37 +1433,40 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1511,14 +1534,17 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
+      <c r="AG15" s="3">
+        <v>0</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="K17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
-        <v>2400</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="V17" s="3">
         <v>1400</v>
       </c>
-      <c r="R17" s="3">
-        <v>2100</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
-      </c>
-      <c r="X17" s="3">
-        <v>1400</v>
       </c>
       <c r="Y17" s="3">
         <v>1400</v>
       </c>
       <c r="Z17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA17" s="3">
         <v>1900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1800</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="N18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R18" s="3">
+        <v>7600</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="AC18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-700</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O18" s="3">
-        <v>200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>7600</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-200</v>
       </c>
       <c r="AE18" s="3">
         <v>-200</v>
       </c>
       <c r="AF18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-600</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,37 +1815,38 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-100</v>
@@ -1821,165 +1855,171 @@
         <v>-100</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>-100</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>100</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
+        <v>100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P21" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
-        <v>200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="R21" s="3">
+        <v>7700</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="W21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="AA21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
-        <v>400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>7700</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="AC21" s="3">
         <v>-300</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>0</v>
-      </c>
       <c r="AE21" s="3">
         <v>0</v>
       </c>
       <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-400</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2059,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="3">
         <v>100</v>
@@ -2070,210 +2110,219 @@
       <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>4</v>
+      <c r="AG22" s="3">
+        <v>100</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-400</v>
       </c>
       <c r="F23" s="3">
         <v>-400</v>
       </c>
       <c r="G23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-300</v>
       </c>
       <c r="AE23" s="3">
         <v>-300</v>
       </c>
       <c r="AF23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-700</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-100</v>
       </c>
       <c r="F24" s="3">
         <v>-100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>-200</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-100</v>
       </c>
       <c r="AB24" s="3">
         <v>-100</v>
       </c>
       <c r="AC24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-100</v>
       </c>
       <c r="AE24" s="3">
         <v>-100</v>
       </c>
       <c r="AF24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-300</v>
       </c>
       <c r="F26" s="3">
         <v>-300</v>
       </c>
       <c r="G26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-100</v>
       </c>
       <c r="X26" s="3">
         <v>-100</v>
       </c>
       <c r="Y26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-200</v>
       </c>
       <c r="AE26" s="3">
         <v>-200</v>
       </c>
       <c r="AF26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-300</v>
       </c>
       <c r="F27" s="3">
         <v>-300</v>
       </c>
       <c r="G27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-100</v>
       </c>
       <c r="X27" s="3">
         <v>-100</v>
       </c>
       <c r="Y27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-200</v>
       </c>
       <c r="AE27" s="3">
         <v>-200</v>
       </c>
       <c r="AF27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2705,14 +2766,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>4</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2724,17 +2785,17 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>100</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>300</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
@@ -2745,25 +2806,28 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>4</v>
+      <c r="AF29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,37 +3025,40 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>100</v>
@@ -2997,165 +3067,171 @@
         <v>100</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>100</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>-100</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-500</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-300</v>
       </c>
       <c r="F33" s="3">
         <v>-300</v>
       </c>
       <c r="G33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-200</v>
       </c>
       <c r="AE33" s="3">
         <v>-200</v>
       </c>
       <c r="AF33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-500</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-300</v>
       </c>
       <c r="F35" s="3">
         <v>-300</v>
       </c>
       <c r="G35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-200</v>
       </c>
       <c r="AE35" s="3">
         <v>-200</v>
       </c>
       <c r="AF35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,129 +3611,133 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2400</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3715,25 +3805,28 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>4</v>
+      <c r="AG42" s="3">
+        <v>0</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
@@ -3745,16 +3838,16 @@
         <v>100</v>
       </c>
       <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
@@ -3772,11 +3865,11 @@
         <v>100</v>
       </c>
       <c r="S43" s="3">
+        <v>100</v>
+      </c>
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
@@ -3784,66 +3877,69 @@
         <v>0</v>
       </c>
       <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>500</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
       <c r="AA43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="3">
         <v>200</v>
       </c>
       <c r="AC43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
       <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
         <v>100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>300</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3911,37 +4007,40 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>4</v>
+      <c r="AG44" s="3">
+        <v>0</v>
       </c>
       <c r="AH44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>500</v>
@@ -3950,37 +4049,37 @@
         <v>500</v>
       </c>
       <c r="M45" s="3">
+        <v>500</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
-      </c>
-      <c r="T45" s="3">
-        <v>300</v>
       </c>
       <c r="U45" s="3">
         <v>300</v>
       </c>
       <c r="V45" s="3">
+        <v>300</v>
+      </c>
+      <c r="W45" s="3">
         <v>500</v>
-      </c>
-      <c r="W45" s="3">
-        <v>300</v>
       </c>
       <c r="X45" s="3">
         <v>300</v>
@@ -3989,57 +4088,60 @@
         <v>300</v>
       </c>
       <c r="Z45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>400</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>300</v>
       </c>
       <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>4</v>
+      <c r="AG45" s="3">
+        <v>300</v>
       </c>
       <c r="AH45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4107,58 +4209,61 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>4</v>
+      <c r="AG46" s="3">
+        <v>0</v>
       </c>
       <c r="AH46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>3700</v>
-      </c>
-      <c r="K47" s="3">
-        <v>2200</v>
       </c>
       <c r="L47" s="3">
         <v>2200</v>
       </c>
       <c r="M47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N47" s="3">
         <v>900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>1000</v>
       </c>
       <c r="O47" s="3">
         <v>1000</v>
       </c>
       <c r="P47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>1300</v>
       </c>
       <c r="R47" s="3">
         <v>1300</v>
@@ -4170,7 +4275,7 @@
         <v>1300</v>
       </c>
       <c r="U47" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="V47" s="3">
         <v>2400</v>
@@ -4179,7 +4284,7 @@
         <v>2400</v>
       </c>
       <c r="X47" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="Y47" s="3">
         <v>2600</v>
@@ -4188,84 +4293,87 @@
         <v>2600</v>
       </c>
       <c r="AA47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AB47" s="3">
         <v>3800</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>4000</v>
       </c>
       <c r="AC47" s="3">
         <v>4000</v>
       </c>
       <c r="AD47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AE47" s="3">
         <v>4400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5500</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="L48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="M48" s="3">
         <v>10600</v>
-      </c>
-      <c r="E48" s="3">
-        <v>10500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>10800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>10700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>10700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>10700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>10500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>10700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>10600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>10500</v>
       </c>
       <c r="N48" s="3">
         <v>10500</v>
       </c>
       <c r="O48" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="P48" s="3">
         <v>10600</v>
       </c>
       <c r="Q48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="R48" s="3">
         <v>10500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>10600</v>
       </c>
       <c r="S48" s="3">
         <v>10600</v>
       </c>
       <c r="T48" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="U48" s="3">
         <v>10700</v>
@@ -4274,7 +4382,7 @@
         <v>10700</v>
       </c>
       <c r="W48" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="X48" s="3">
         <v>10900</v>
@@ -4283,34 +4391,37 @@
         <v>10900</v>
       </c>
       <c r="Z48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AA48" s="3">
         <v>20400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>21100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>21300</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4401,14 +4512,17 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>4</v>
+      <c r="AG49" s="3">
+        <v>0</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,41 +4720,44 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
+        <v>300</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
-        <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -4651,58 +4771,61 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>1400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1700</v>
-      </c>
-      <c r="W52" s="3">
-        <v>1600</v>
       </c>
       <c r="X52" s="3">
         <v>1600</v>
       </c>
       <c r="Y52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Z52" s="3">
         <v>10400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5800</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>1000</v>
       </c>
       <c r="AD52" s="3">
         <v>1000</v>
       </c>
       <c r="AE52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1100</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E54" s="3">
         <v>23400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>24700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21400</v>
-      </c>
-      <c r="L54" s="3">
-        <v>21600</v>
       </c>
       <c r="M54" s="3">
         <v>21600</v>
       </c>
       <c r="N54" s="3">
+        <v>21600</v>
+      </c>
+      <c r="O54" s="3">
         <v>22500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28100</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>28300</v>
       </c>
       <c r="AC54" s="3">
         <v>28300</v>
       </c>
       <c r="AD54" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AE54" s="3">
         <v>30000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>30900</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4978,19 +5109,19 @@
         <v>500</v>
       </c>
       <c r="E57" s="3">
+        <v>500</v>
+      </c>
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
       </c>
       <c r="H57" s="3">
         <v>500</v>
       </c>
       <c r="I57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J57" s="3">
         <v>400</v>
@@ -5002,22 +5133,22 @@
         <v>400</v>
       </c>
       <c r="M57" s="3">
+        <v>400</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>400</v>
       </c>
       <c r="P57" s="3">
         <v>400</v>
       </c>
       <c r="Q57" s="3">
+        <v>400</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>300</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
@@ -5026,69 +5157,72 @@
         <v>300</v>
       </c>
       <c r="U57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V57" s="3">
         <v>200</v>
       </c>
       <c r="W57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X57" s="3">
         <v>300</v>
       </c>
       <c r="Y57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z57" s="3">
         <v>200</v>
       </c>
       <c r="AA57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB57" s="3">
         <v>300</v>
       </c>
       <c r="AC57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD57" s="3">
         <v>200</v>
       </c>
       <c r="AE57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF57" s="3">
         <v>300</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
+      <c r="AG57" s="3">
+        <v>300</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -5112,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>500</v>
@@ -5121,7 +5255,7 @@
         <v>500</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5139,16 +5273,16 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>300</v>
       </c>
       <c r="AB58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC58" s="3">
         <v>200</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>300</v>
       </c>
       <c r="AD58" s="3">
         <v>300</v>
@@ -5159,135 +5293,141 @@
       <c r="AF58" s="3">
         <v>300</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>4</v>
+      <c r="AG58" s="3">
+        <v>300</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="M59" s="3">
+        <v>200</v>
+      </c>
+      <c r="N59" s="3">
+        <v>300</v>
+      </c>
+      <c r="O59" s="3">
+        <v>500</v>
+      </c>
+      <c r="P59" s="3">
         <v>400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>500</v>
-      </c>
-      <c r="O59" s="3">
-        <v>400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>300</v>
       </c>
       <c r="Q59" s="3">
         <v>300</v>
       </c>
       <c r="R59" s="3">
+        <v>300</v>
+      </c>
+      <c r="S59" s="3">
         <v>500</v>
-      </c>
-      <c r="S59" s="3">
-        <v>300</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
       </c>
       <c r="U59" s="3">
+        <v>300</v>
+      </c>
+      <c r="V59" s="3">
         <v>400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4800</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5355,14 +5495,17 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>4</v>
+      <c r="AG60" s="3">
+        <v>0</v>
       </c>
       <c r="AH60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5424,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>100</v>
@@ -5433,115 +5576,118 @@
         <v>100</v>
       </c>
       <c r="Z61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA61" s="3">
         <v>6000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6400</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>6500</v>
       </c>
       <c r="AF61" s="3">
         <v>6500</v>
       </c>
       <c r="AG61" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
-      </c>
-      <c r="K62" s="3">
-        <v>400</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
       </c>
       <c r="M62" s="3">
+        <v>400</v>
+      </c>
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1800</v>
-      </c>
-      <c r="U62" s="3">
-        <v>1700</v>
       </c>
       <c r="V62" s="3">
         <v>1700</v>
       </c>
       <c r="W62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X62" s="3">
         <v>2700</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
         <v>6200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC62" s="3">
         <v>3100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,8 +6006,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5860,97 +6018,100 @@
         <v>2300</v>
       </c>
       <c r="E66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2700</v>
-      </c>
-      <c r="P66" s="3">
-        <v>3400</v>
       </c>
       <c r="Q66" s="3">
         <v>3400</v>
       </c>
       <c r="R66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S66" s="3">
         <v>2900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12400</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6273,14 +6441,17 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-      <c r="AG70" s="3" t="s">
-        <v>4</v>
+      <c r="AG70" s="3">
+        <v>0</v>
       </c>
       <c r="AH70" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E72" s="3">
         <v>3500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2100</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-1900</v>
       </c>
       <c r="T72" s="3">
         <v>-1900</v>
       </c>
       <c r="U72" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="V72" s="3">
         <v>-1100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1900</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E76" s="3">
         <v>21100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15000</v>
-      </c>
-      <c r="S76" s="3">
-        <v>14600</v>
       </c>
       <c r="T76" s="3">
         <v>14600</v>
       </c>
       <c r="U76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="V76" s="3">
         <v>15400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18500</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-500</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-300</v>
       </c>
       <c r="F81" s="3">
         <v>-300</v>
       </c>
       <c r="G81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-200</v>
       </c>
       <c r="AE81" s="3">
         <v>-200</v>
       </c>
       <c r="AF81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7271,7 +7470,7 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -7294,14 +7493,17 @@
       <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
+      <c r="AG83" s="3">
+        <v>200</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7799,97 +8016,100 @@
         <v>200</v>
       </c>
       <c r="E89" s="3">
+        <v>200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-300</v>
       </c>
       <c r="G89" s="3">
         <v>-300</v>
       </c>
       <c r="H89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I89" s="3">
         <v>4600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>400</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="Z89" s="3">
         <v>-400</v>
       </c>
       <c r="AA89" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="AB89" s="3">
         <v>-100</v>
       </c>
       <c r="AC89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
+      <c r="AG89" s="3">
+        <v>0</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,73 +8144,74 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
       </c>
       <c r="X91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -7999,11 +8220,11 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
@@ -8014,16 +8235,19 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,53 +8445,56 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -8272,52 +8502,55 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>900</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>3200</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>1100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>600</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8585,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,19 +8987,22 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
         <v>0</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -8764,11 +9010,11 @@
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8786,20 +9032,20 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -8807,13 +9053,13 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="3">
         <v>-100</v>
@@ -8834,39 +9080,42 @@
         <v>-100</v>
       </c>
       <c r="AF100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8934,108 +9183,114 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>4</v>
+      <c r="AG101" s="3">
+        <v>0</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -656,284 +656,298 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F8" s="3">
         <v>2600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>1200</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E9" s="3">
         <v>2000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>300</v>
-      </c>
-      <c r="M9" s="3">
-        <v>300</v>
       </c>
       <c r="N9" s="3">
         <v>300</v>
@@ -942,7 +956,7 @@
         <v>300</v>
       </c>
       <c r="P9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q9" s="3">
         <v>300</v>
@@ -954,22 +968,22 @@
         <v>300</v>
       </c>
       <c r="T9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="U9" s="3">
         <v>300</v>
       </c>
       <c r="V9" s="3">
+        <v>200</v>
+      </c>
+      <c r="W9" s="3">
         <v>300</v>
-      </c>
-      <c r="W9" s="3">
-        <v>400</v>
       </c>
       <c r="X9" s="3">
         <v>300</v>
       </c>
       <c r="Y9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Z9" s="3">
         <v>300</v>
@@ -984,126 +998,138 @@
         <v>300</v>
       </c>
       <c r="AD9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AE9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AF9" s="3">
         <v>400</v>
       </c>
       <c r="AG9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI9" s="3">
         <v>600</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI9" s="3" t="s">
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-300</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>4600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>8600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>600</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1375,14 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,47 +1393,47 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1406,11 +1446,11 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1436,14 +1476,20 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1469,10 +1515,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1537,14 +1583,20 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI15" s="3" t="s">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1800</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
         <v>100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>4100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>7600</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-600</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,13 +1882,15 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-100</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1842,44 +1910,44 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -1888,16 +1956,16 @@
         <v>-100</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -1906,120 +1974,132 @@
         <v>100</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AH20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>400</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>7700</v>
       </c>
       <c r="S21" s="3">
         <v>-200</v>
       </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="U21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-500</v>
       </c>
-      <c r="AE21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
       <c r="AG21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-400</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2102,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="3">
         <v>100</v>
@@ -2113,216 +2193,234 @@
       <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AH22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>300</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>7600</v>
       </c>
       <c r="S23" s="3">
         <v>-300</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="U23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-700</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AJ23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK23" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>1900</v>
       </c>
       <c r="S24" s="3">
         <v>-100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="U24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-200</v>
       </c>
       <c r="AE24" s="3">
         <v>-100</v>
       </c>
       <c r="AF24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-200</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI24" s="3" t="s">
+      <c r="AJ24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-600</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P26" s="3">
-        <v>200</v>
       </c>
       <c r="Q26" s="3">
         <v>-200</v>
       </c>
       <c r="R26" s="3">
-        <v>5600</v>
+        <v>200</v>
       </c>
       <c r="S26" s="3">
         <v>-200</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="U26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-200</v>
       </c>
       <c r="AC26" s="3">
         <v>-400</v>
       </c>
       <c r="AD26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-400</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK26" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P27" s="3">
-        <v>200</v>
       </c>
       <c r="Q27" s="3">
         <v>-200</v>
       </c>
       <c r="R27" s="3">
-        <v>5600</v>
+        <v>200</v>
       </c>
       <c r="S27" s="3">
         <v>-200</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="U27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-200</v>
       </c>
       <c r="AC27" s="3">
         <v>-400</v>
       </c>
       <c r="AD27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-400</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK27" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2769,17 +2891,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2788,20 +2910,20 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>300</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
@@ -2809,25 +2931,31 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK29" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,13 +3162,19 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>100</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -3054,44 +3194,44 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -3100,16 +3240,16 @@
         <v>100</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -3118,120 +3258,132 @@
         <v>-100</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AH32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P33" s="3">
-        <v>200</v>
       </c>
       <c r="Q33" s="3">
         <v>-200</v>
       </c>
       <c r="R33" s="3">
-        <v>5600</v>
+        <v>200</v>
       </c>
       <c r="S33" s="3">
         <v>-200</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="U33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-400</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK33" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P35" s="3">
-        <v>200</v>
       </c>
       <c r="Q35" s="3">
         <v>-200</v>
       </c>
       <c r="R35" s="3">
-        <v>5600</v>
+        <v>200</v>
       </c>
       <c r="S35" s="3">
         <v>-200</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="U35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-400</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK35" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,139 +3784,147 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>11000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>11200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3600</v>
-      </c>
-      <c r="U41" s="3">
-        <v>3200</v>
-      </c>
-      <c r="V41" s="3">
-        <v>2500</v>
       </c>
       <c r="W41" s="3">
         <v>3200</v>
       </c>
       <c r="X41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Z41" s="3">
         <v>5700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>5300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>3100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2400</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI41" s="3" t="s">
+      <c r="AJ41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F42" s="3">
         <v>2100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>4300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>5000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3808,19 +3988,25 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI42" s="3" t="s">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK42" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -3832,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
@@ -3841,19 +4027,19 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
       </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P43" s="3">
         <v>100</v>
@@ -3868,55 +4054,61 @@
         <v>100</v>
       </c>
       <c r="T43" s="3">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3">
+        <v>100</v>
+      </c>
+      <c r="V43" s="3">
         <v>600</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>500</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>200</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
       <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
         <v>100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>300</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI43" s="3" t="s">
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK43" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3941,11 +4133,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4010,94 +4202,100 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI44" s="3" t="s">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK44" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>500</v>
       </c>
       <c r="M45" s="3">
         <v>500</v>
       </c>
       <c r="N45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="O45" s="3">
         <v>500</v>
       </c>
       <c r="P45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q45" s="3">
         <v>500</v>
       </c>
       <c r="R45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S45" s="3">
         <v>500</v>
       </c>
       <c r="T45" s="3">
+        <v>300</v>
+      </c>
+      <c r="U45" s="3">
+        <v>500</v>
+      </c>
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
-      </c>
-      <c r="V45" s="3">
-        <v>300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>500</v>
       </c>
       <c r="X45" s="3">
         <v>300</v>
       </c>
       <c r="Y45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="Z45" s="3">
         <v>300</v>
       </c>
       <c r="AA45" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AB45" s="3">
         <v>300</v>
       </c>
       <c r="AC45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD45" s="3">
         <v>300</v>
@@ -4109,46 +4307,52 @@
         <v>300</v>
       </c>
       <c r="AG45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH45" s="3">
         <v>300</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AI45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>13000</v>
+        <v>11700</v>
       </c>
       <c r="E46" s="3">
         <v>12800</v>
       </c>
       <c r="F46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G46" s="3">
         <v>12800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I46" s="3">
         <v>12900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9300</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4212,14 +4416,20 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI46" s="3" t="s">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK46" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,32 +4454,32 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>3700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1200</v>
-      </c>
-      <c r="R47" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S47" s="3">
-        <v>1300</v>
       </c>
       <c r="T47" s="3">
         <v>1300</v>
@@ -4278,150 +4488,162 @@
         <v>1300</v>
       </c>
       <c r="V47" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="W47" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="X47" s="3">
         <v>2400</v>
       </c>
       <c r="Y47" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="Z47" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="AA47" s="3">
         <v>2600</v>
       </c>
       <c r="AB47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AD47" s="3">
         <v>3800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>4000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>4000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>4400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>5100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>5500</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI47" s="3" t="s">
+      <c r="AJ47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK47" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="E48" s="3">
         <v>9100</v>
       </c>
       <c r="F48" s="3">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="G48" s="3">
-        <v>9300</v>
+        <v>9100</v>
       </c>
       <c r="H48" s="3">
         <v>9200</v>
       </c>
       <c r="I48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J48" s="3">
         <v>9200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="L48" s="3">
         <v>9100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>10500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>10700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>10600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>10500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>10500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>10600</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>10600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>10500</v>
       </c>
       <c r="S48" s="3">
         <v>10600</v>
       </c>
       <c r="T48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="U48" s="3">
         <v>10600</v>
       </c>
-      <c r="U48" s="3">
-        <v>10700</v>
-      </c>
       <c r="V48" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="W48" s="3">
         <v>10700</v>
       </c>
       <c r="X48" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="Y48" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="Z48" s="3">
         <v>10900</v>
       </c>
       <c r="AA48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AC48" s="3">
         <v>20400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>20600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>16000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>20800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>20900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>21100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>21300</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI48" s="3" t="s">
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4515,14 +4737,20 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI49" s="3" t="s">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4957,14 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4735,13 +4975,13 @@
         <v>1500</v>
       </c>
       <c r="F52" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G52" s="3">
         <v>1500</v>
       </c>
       <c r="H52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="I52" s="3">
         <v>1500</v>
@@ -4750,19 +4990,19 @@
         <v>1500</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="L52" s="3">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4774,58 +5014,64 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>1400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>10400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>5800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>1000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1100</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI52" s="3" t="s">
+      <c r="AJ52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>23600</v>
+        <v>22200</v>
       </c>
       <c r="E54" s="3">
         <v>23400</v>
       </c>
       <c r="F54" s="3">
+        <v>23600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>23400</v>
+      </c>
+      <c r="H54" s="3">
         <v>23300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>23700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>24400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>24700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>20100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>20700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>21400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>21600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>21600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>22500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>23200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>23700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>24000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>17900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>18100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>17600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>17900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>18600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>21000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>21200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>26400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>27000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>28100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>28300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>28300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>30000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>30700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>30900</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI54" s="3" t="s">
+      <c r="AJ54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,34 +5360,36 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>400</v>
@@ -5136,73 +5398,79 @@
         <v>400</v>
       </c>
       <c r="N57" s="3">
+        <v>400</v>
+      </c>
+      <c r="O57" s="3">
+        <v>400</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>300</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
       </c>
       <c r="V57" s="3">
+        <v>300</v>
+      </c>
+      <c r="W57" s="3">
+        <v>300</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>300</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI57" s="3" t="s">
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5249,19 +5517,19 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>500</v>
       </c>
       <c r="U58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5276,19 +5544,19 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>300</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>200</v>
       </c>
       <c r="AD58" s="3">
         <v>300</v>
       </c>
       <c r="AE58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF58" s="3">
         <v>300</v>
@@ -5296,145 +5564,157 @@
       <c r="AG58" s="3">
         <v>300</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI58" s="3" t="s">
+      <c r="AH58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK58" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>300</v>
-      </c>
-      <c r="S59" s="3">
-        <v>500</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
       </c>
       <c r="U59" s="3">
+        <v>500</v>
+      </c>
+      <c r="V59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
+        <v>300</v>
+      </c>
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>3200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>3900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>3600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>4400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>5000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>4800</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI59" s="3" t="s">
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E60" s="3">
         <v>1000</v>
       </c>
       <c r="F60" s="3">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="G60" s="3">
         <v>1000</v>
       </c>
       <c r="H60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I60" s="3">
         <v>900</v>
       </c>
       <c r="J60" s="3">
+        <v>800</v>
+      </c>
+      <c r="K60" s="3">
+        <v>900</v>
+      </c>
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5498,14 +5778,20 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI60" s="3" t="s">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK60" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5570,43 +5856,49 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="3">
         <v>100</v>
       </c>
       <c r="AA61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC61" s="3">
         <v>6000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>6100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>3300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>6300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>6400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>6500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>6500</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5631,69 +5923,69 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2700</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
         <v>6200</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE62" s="3">
         <v>3100</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5706,8 +5998,14 @@
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>4100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>9600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>9700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>10900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>11000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>10600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>11500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>12300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>12400</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI66" s="3" t="s">
+      <c r="AJ66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6444,14 +6780,20 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-      <c r="AH70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI70" s="3" t="s">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK70" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,49 +6893,55 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E72" s="3">
         <v>3700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G72" s="3">
         <v>3500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2800</v>
-      </c>
-      <c r="O72" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P72" s="3">
-        <v>3500</v>
       </c>
       <c r="Q72" s="3">
         <v>3300</v>
@@ -6602,58 +6950,64 @@
         <v>3500</v>
       </c>
       <c r="S72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T72" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U72" s="3">
         <v>-2100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-1900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-1900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1900</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>21600</v>
+      </c>
+      <c r="F76" s="3">
         <v>21300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>21100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>21600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>22100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>22000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>18900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>19400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>20200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>20800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>20500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>20200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>20600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>15000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>14600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>15900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>16900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>17100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>16700</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>17300</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>17200</v>
       </c>
       <c r="AC76" s="3">
         <v>17300</v>
       </c>
       <c r="AD76" s="3">
+        <v>17200</v>
+      </c>
+      <c r="AE76" s="3">
+        <v>17300</v>
+      </c>
+      <c r="AF76" s="3">
         <v>17700</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>18500</v>
-      </c>
-      <c r="AF76" s="3">
-        <v>18400</v>
       </c>
       <c r="AG76" s="3">
         <v>18500</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI76" s="3" t="s">
+      <c r="AH76" s="3">
+        <v>18400</v>
+      </c>
+      <c r="AI76" s="3">
+        <v>18500</v>
+      </c>
+      <c r="AJ76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P81" s="3">
-        <v>200</v>
       </c>
       <c r="Q81" s="3">
         <v>-200</v>
       </c>
       <c r="R81" s="3">
-        <v>5600</v>
+        <v>200</v>
       </c>
       <c r="S81" s="3">
         <v>-200</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="U81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-400</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK81" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7797,10 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7473,10 +7871,10 @@
         <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
@@ -7496,14 +7894,20 @@
       <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AH83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>7700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-3000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>400</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>200</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8585,10 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8154,16 +8596,16 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -8172,65 +8614,65 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
@@ -8238,16 +8680,22 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8902,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1600</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>900</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>3200</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>1100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>300</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>600</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>400</v>
       </c>
       <c r="AG94" s="3">
         <v>600</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AH94" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +9052,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,11 +9080,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,37 +9476,43 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
         <v>0</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9035,28 +9527,28 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -9065,7 +9557,7 @@
         <v>-100</v>
       </c>
       <c r="AA100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB100" s="3">
         <v>-100</v>
@@ -9083,16 +9575,22 @@
         <v>-100</v>
       </c>
       <c r="AG100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,11 +9615,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9186,111 +9684,123 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI101" s="3" t="s">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-200</v>
       </c>
       <c r="Q102" s="3">
         <v>-600</v>
       </c>
       <c r="R102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T102" s="3">
         <v>7600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -1889,8 +1889,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-100</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1997,7 +1997,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-600</v>
+        <v>-800</v>
       </c>
       <c r="E21" s="3">
         <v>-100</v>
@@ -3173,8 +3173,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>100</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -656,301 +656,307 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1000</v>
       </c>
       <c r="H8" s="3">
         <v>1000</v>
       </c>
       <c r="I8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2000</v>
       </c>
       <c r="F9" s="3">
         <v>2000</v>
       </c>
       <c r="G9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
-      </c>
-      <c r="N9" s="3">
-        <v>300</v>
       </c>
       <c r="O9" s="3">
         <v>300</v>
@@ -962,31 +968,31 @@
         <v>300</v>
       </c>
       <c r="R9" s="3">
+        <v>300</v>
+      </c>
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>200</v>
-      </c>
-      <c r="W9" s="3">
-        <v>300</v>
       </c>
       <c r="X9" s="3">
         <v>300</v>
       </c>
       <c r="Y9" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z9" s="3">
         <v>400</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>300</v>
       </c>
       <c r="AA9" s="3">
         <v>300</v>
@@ -1004,7 +1010,7 @@
         <v>300</v>
       </c>
       <c r="AF9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AG9" s="3">
         <v>400</v>
@@ -1013,123 +1019,129 @@
         <v>400</v>
       </c>
       <c r="AI9" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>600</v>
       </c>
-      <c r="AJ9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-300</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>600</v>
       </c>
-      <c r="AJ10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1399,44 +1418,44 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1452,8 +1471,8 @@
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1482,14 +1501,17 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>4</v>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1521,7 +1543,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1589,14 +1611,17 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>4</v>
+      <c r="AJ15" s="3">
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1900</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1400</v>
       </c>
       <c r="AB17" s="3">
         <v>1400</v>
       </c>
       <c r="AC17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD17" s="3">
         <v>1900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK17" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL17" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>4100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7600</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-700</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-200</v>
       </c>
       <c r="AH18" s="3">
         <v>-200</v>
       </c>
       <c r="AI18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,13 +1916,14 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1901,8 +1934,8 @@
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
@@ -1916,14 +1949,14 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>-100</v>
@@ -1932,179 +1965,185 @@
         <v>-100</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>-100</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="3">
         <v>100</v>
       </c>
       <c r="AI20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-200</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-300</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-500</v>
       </c>
-      <c r="AG21" s="3">
-        <v>0</v>
-      </c>
       <c r="AH21" s="3">
         <v>0</v>
       </c>
       <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -2115,8 +2154,8 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -2188,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="AF22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="3">
         <v>100</v>
@@ -2199,228 +2238,237 @@
       <c r="AI22" s="3">
         <v>100</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>4</v>
+      <c r="AJ22" s="3">
+        <v>100</v>
       </c>
       <c r="AK22" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL22" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-400</v>
       </c>
       <c r="I23" s="3">
         <v>-400</v>
       </c>
       <c r="J23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-300</v>
       </c>
       <c r="AH23" s="3">
         <v>-300</v>
       </c>
       <c r="AI23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ23" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK23" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL23" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
       </c>
       <c r="I24" s="3">
         <v>-100</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
         <v>-200</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-100</v>
       </c>
       <c r="AE24" s="3">
         <v>-100</v>
       </c>
       <c r="AF24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>-100</v>
       </c>
       <c r="AH24" s="3">
         <v>-100</v>
       </c>
       <c r="AI24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK24" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL24" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-300</v>
       </c>
       <c r="I26" s="3">
         <v>-300</v>
       </c>
       <c r="J26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-100</v>
       </c>
       <c r="AA26" s="3">
         <v>-100</v>
       </c>
       <c r="AB26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>-200</v>
       </c>
       <c r="AH26" s="3">
         <v>-200</v>
       </c>
       <c r="AI26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK26" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL26" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-300</v>
       </c>
       <c r="I27" s="3">
         <v>-300</v>
       </c>
       <c r="J27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-100</v>
       </c>
       <c r="AA27" s="3">
         <v>-100</v>
       </c>
       <c r="AB27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-200</v>
       </c>
       <c r="AH27" s="3">
         <v>-200</v>
       </c>
       <c r="AI27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK27" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL27" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2897,14 +2957,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2916,17 +2976,17 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>300</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
@@ -2937,25 +2997,28 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-200</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>4</v>
+      <c r="AI29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,13 +3234,16 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -3185,8 +3254,8 @@
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
@@ -3200,14 +3269,14 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>100</v>
@@ -3216,174 +3285,180 @@
         <v>100</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>100</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="3">
         <v>-100</v>
       </c>
       <c r="AI32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-300</v>
       </c>
       <c r="I33" s="3">
         <v>-300</v>
       </c>
       <c r="J33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-200</v>
       </c>
       <c r="AH33" s="3">
         <v>-200</v>
       </c>
       <c r="AI33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK33" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL33" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-300</v>
       </c>
       <c r="I35" s="3">
         <v>-300</v>
       </c>
       <c r="J35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-200</v>
       </c>
       <c r="AH35" s="3">
         <v>-200</v>
       </c>
       <c r="AI35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK35" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL35" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,148 +3871,152 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E41" s="3">
         <v>8800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2300</v>
+        <v>2800</v>
       </c>
       <c r="E42" s="3">
         <v>2300</v>
       </c>
       <c r="F42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3994,14 +4083,17 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>4</v>
+      <c r="AJ42" s="3">
+        <v>0</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4012,16 +4104,16 @@
         <v>100</v>
       </c>
       <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>100</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -4033,16 +4125,16 @@
         <v>100</v>
       </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
         <v>100</v>
@@ -4060,11 +4152,11 @@
         <v>100</v>
       </c>
       <c r="V43" s="3">
+        <v>100</v>
+      </c>
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
@@ -4072,43 +4164,46 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>500</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
-      </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
       <c r="AD43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="3">
         <v>200</v>
       </c>
       <c r="AF43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
       </c>
       <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
         <v>100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>300</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4139,8 +4234,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4208,14 +4303,17 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>4</v>
+      <c r="AJ44" s="3">
+        <v>0</v>
       </c>
       <c r="AK44" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4223,31 +4321,31 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
       </c>
       <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>500</v>
       </c>
       <c r="N45" s="3">
         <v>500</v>
@@ -4256,37 +4354,37 @@
         <v>500</v>
       </c>
       <c r="P45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
-      </c>
-      <c r="W45" s="3">
-        <v>300</v>
       </c>
       <c r="X45" s="3">
         <v>300</v>
       </c>
       <c r="Y45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z45" s="3">
         <v>500</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>300</v>
       </c>
       <c r="AA45" s="3">
         <v>300</v>
@@ -4295,67 +4393,70 @@
         <v>300</v>
       </c>
       <c r="AC45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD45" s="3">
         <v>500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>300</v>
       </c>
       <c r="AI45" s="3">
         <v>300</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>4</v>
+      <c r="AJ45" s="3">
+        <v>300</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E46" s="3">
         <v>11700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>12800</v>
       </c>
       <c r="H46" s="3">
         <v>12800</v>
       </c>
       <c r="I46" s="3">
+        <v>12800</v>
+      </c>
+      <c r="J46" s="3">
         <v>12900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9300</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4422,14 +4523,17 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>4</v>
+      <c r="AJ46" s="3">
+        <v>0</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4460,29 +4564,29 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>3700</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2200</v>
       </c>
       <c r="O47" s="3">
         <v>2200</v>
       </c>
       <c r="P47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>900</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>1000</v>
       </c>
       <c r="R47" s="3">
         <v>1000</v>
       </c>
       <c r="S47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T47" s="3">
         <v>1200</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1300</v>
       </c>
       <c r="U47" s="3">
         <v>1300</v>
@@ -4494,7 +4598,7 @@
         <v>1300</v>
       </c>
       <c r="X47" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="Y47" s="3">
         <v>2400</v>
@@ -4503,7 +4607,7 @@
         <v>2400</v>
       </c>
       <c r="AA47" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="AB47" s="3">
         <v>2600</v>
@@ -4512,39 +4616,42 @@
         <v>2600</v>
       </c>
       <c r="AD47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AE47" s="3">
         <v>3800</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>4000</v>
       </c>
       <c r="AF47" s="3">
         <v>4000</v>
       </c>
       <c r="AG47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AH47" s="3">
         <v>4400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E48" s="3">
         <v>9000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>9100</v>
       </c>
       <c r="F48" s="3">
         <v>9100</v>
@@ -4553,52 +4660,52 @@
         <v>9100</v>
       </c>
       <c r="H48" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I48" s="3">
         <v>9200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>9200</v>
       </c>
       <c r="K48" s="3">
         <v>9200</v>
       </c>
       <c r="L48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="M48" s="3">
         <v>9100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>10500</v>
       </c>
       <c r="Q48" s="3">
         <v>10500</v>
       </c>
       <c r="R48" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="S48" s="3">
         <v>10600</v>
       </c>
       <c r="T48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="U48" s="3">
         <v>10500</v>
-      </c>
-      <c r="U48" s="3">
-        <v>10600</v>
       </c>
       <c r="V48" s="3">
         <v>10600</v>
       </c>
       <c r="W48" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="X48" s="3">
         <v>10700</v>
@@ -4607,7 +4714,7 @@
         <v>10700</v>
       </c>
       <c r="Z48" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="AA48" s="3">
         <v>10900</v>
@@ -4616,34 +4723,37 @@
         <v>10900</v>
       </c>
       <c r="AC48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AD48" s="3">
         <v>20400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>16000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>21100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>21300</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4743,14 +4853,17 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>4</v>
+      <c r="AJ49" s="3">
+        <v>0</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4981,10 +5100,10 @@
         <v>1500</v>
       </c>
       <c r="H52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I52" s="3">
         <v>1400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1500</v>
       </c>
       <c r="J52" s="3">
         <v>1500</v>
@@ -4996,17 +5115,17 @@
         <v>1500</v>
       </c>
       <c r="M52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -5020,58 +5139,61 @@
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>1400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1700</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1600</v>
       </c>
       <c r="AA52" s="3">
         <v>1600</v>
       </c>
       <c r="AB52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC52" s="3">
         <v>10400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5800</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>1000</v>
       </c>
       <c r="AG52" s="3">
         <v>1000</v>
       </c>
       <c r="AH52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI52" s="3">
         <v>1200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E54" s="3">
         <v>22200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21400</v>
-      </c>
-      <c r="O54" s="3">
-        <v>21600</v>
       </c>
       <c r="P54" s="3">
         <v>21600</v>
       </c>
       <c r="Q54" s="3">
+        <v>21600</v>
+      </c>
+      <c r="R54" s="3">
         <v>22500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>24000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>26400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28100</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>28300</v>
       </c>
       <c r="AF54" s="3">
         <v>28300</v>
       </c>
       <c r="AG54" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AH54" s="3">
         <v>30000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>30900</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,37 +5491,38 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>500</v>
       </c>
       <c r="K57" s="3">
         <v>500</v>
       </c>
       <c r="L57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M57" s="3">
         <v>400</v>
@@ -5404,22 +5534,22 @@
         <v>400</v>
       </c>
       <c r="P57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>300</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
@@ -5428,49 +5558,52 @@
         <v>300</v>
       </c>
       <c r="X57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y57" s="3">
         <v>200</v>
       </c>
       <c r="Z57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA57" s="3">
         <v>300</v>
       </c>
       <c r="AB57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
       </c>
       <c r="AD57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE57" s="3">
         <v>300</v>
       </c>
       <c r="AF57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AG57" s="3">
         <v>200</v>
       </c>
       <c r="AH57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AI57" s="3">
         <v>300</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>4</v>
+      <c r="AJ57" s="3">
+        <v>300</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5523,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>500</v>
@@ -5532,7 +5665,7 @@
         <v>500</v>
       </c>
       <c r="W58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5550,16 +5683,16 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>300</v>
       </c>
       <c r="AE58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF58" s="3">
         <v>200</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>300</v>
       </c>
       <c r="AG58" s="3">
         <v>300</v>
@@ -5570,25 +5703,28 @@
       <c r="AI58" s="3">
         <v>300</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>4</v>
+      <c r="AJ58" s="3">
+        <v>300</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
@@ -5596,11 +5732,11 @@
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -5608,116 +5744,119 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
-      </c>
-      <c r="S59" s="3">
-        <v>300</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
       </c>
       <c r="U59" s="3">
+        <v>300</v>
+      </c>
+      <c r="V59" s="3">
         <v>500</v>
-      </c>
-      <c r="V59" s="3">
-        <v>300</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
       </c>
       <c r="X59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5784,14 +5923,17 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>4</v>
+      <c r="AJ60" s="3">
+        <v>0</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5862,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA61" s="3">
         <v>100</v>
@@ -5871,34 +6013,37 @@
         <v>100</v>
       </c>
       <c r="AC61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD61" s="3">
         <v>6000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6400</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>6500</v>
       </c>
       <c r="AI61" s="3">
         <v>6500</v>
       </c>
       <c r="AJ61" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5929,66 +6074,66 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>200</v>
-      </c>
-      <c r="N62" s="3">
-        <v>400</v>
       </c>
       <c r="O62" s="3">
         <v>400</v>
       </c>
       <c r="P62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1800</v>
-      </c>
-      <c r="X62" s="3">
-        <v>1700</v>
       </c>
       <c r="Y62" s="3">
         <v>1700</v>
       </c>
       <c r="Z62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA62" s="3">
         <v>2700</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
       <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
         <v>6200</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3">
         <v>3100</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
@@ -6004,8 +6149,11 @@
       <c r="AK62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1800</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2300</v>
       </c>
       <c r="G66" s="3">
         <v>2300</v>
       </c>
       <c r="H66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I66" s="3">
         <v>1700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2700</v>
-      </c>
-      <c r="S66" s="3">
-        <v>3400</v>
       </c>
       <c r="T66" s="3">
         <v>3400</v>
       </c>
       <c r="U66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V66" s="3">
         <v>2900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6786,14 +6953,17 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
-      <c r="AJ70" s="3" t="s">
-        <v>4</v>
+      <c r="AJ70" s="3">
+        <v>0</v>
       </c>
       <c r="AK70" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL70" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E72" s="3">
         <v>3100</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3700</v>
       </c>
       <c r="F72" s="3">
         <v>3700</v>
       </c>
       <c r="G72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H72" s="3">
         <v>3500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2100</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-1900</v>
       </c>
       <c r="W72" s="3">
         <v>-1900</v>
       </c>
       <c r="X72" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E76" s="3">
         <v>21000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15000</v>
-      </c>
-      <c r="V76" s="3">
-        <v>14600</v>
       </c>
       <c r="W76" s="3">
         <v>14600</v>
       </c>
       <c r="X76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="Y76" s="3">
         <v>15400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18500</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-300</v>
       </c>
       <c r="I81" s="3">
         <v>-300</v>
       </c>
       <c r="J81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-200</v>
       </c>
       <c r="AH81" s="3">
         <v>-200</v>
       </c>
       <c r="AI81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK81" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL81" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7877,7 +8075,7 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>200</v>
@@ -7900,14 +8098,17 @@
       <c r="AI83" s="3">
         <v>200</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>4</v>
+      <c r="AJ83" s="3">
+        <v>200</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>200</v>
       </c>
       <c r="G89" s="3">
         <v>200</v>
       </c>
       <c r="H89" s="3">
+        <v>200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-200</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-300</v>
       </c>
       <c r="J89" s="3">
         <v>-300</v>
       </c>
       <c r="K89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L89" s="3">
         <v>4600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>400</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AC89" s="3">
         <v>-400</v>
       </c>
       <c r="AD89" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="AE89" s="3">
         <v>-100</v>
       </c>
       <c r="AF89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>200</v>
       </c>
-      <c r="AI89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ89" s="3" t="s">
-        <v>4</v>
+      <c r="AJ89" s="3">
+        <v>0</v>
       </c>
       <c r="AK89" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,13 +8806,14 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -8602,67 +8822,67 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-200</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8671,11 +8891,11 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
@@ -8686,16 +8906,19 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK91" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,62 +9134,65 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1600</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -8971,52 +9200,55 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>900</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>3200</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>1100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>600</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK94" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9086,8 +9319,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9496,26 +9741,26 @@
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
+      <c r="G100" s="3">
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9533,20 +9778,20 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -9554,13 +9799,13 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC100" s="3">
         <v>-100</v>
@@ -9581,16 +9826,19 @@
         <v>-100</v>
       </c>
       <c r="AI100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>100</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9621,8 +9869,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9690,117 +9938,123 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>4</v>
+      <c r="AJ101" s="3">
+        <v>0</v>
       </c>
       <c r="AK101" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-400</v>
       </c>
       <c r="F102" s="3">
         <v>-400</v>
       </c>
       <c r="G102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>700</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -656,343 +656,364 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45869</v>
+      </c>
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G8" s="3">
         <v>1300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>2600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>2600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>5900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>2200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>9000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>2100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>1800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>1700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
         <v>1800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AE8" s="3">
         <v>800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3">
         <v>700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AG8" s="3">
         <v>1500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AH8" s="3">
         <v>1800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AI8" s="3">
         <v>900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AJ8" s="3">
         <v>800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AK8" s="3">
         <v>1700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AL8" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AM8" s="3">
         <v>1200</v>
       </c>
-      <c r="AK8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL8" s="3" t="s">
+      <c r="AN8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="E9" s="3">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="F9" s="3">
         <v>2000</v>
       </c>
       <c r="G9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I9" s="3">
         <v>2000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1200</v>
       </c>
       <c r="J9" s="3">
         <v>2000</v>
       </c>
       <c r="K9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N9" s="3">
         <v>2200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>1400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>300</v>
-      </c>
-      <c r="P9" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>300</v>
       </c>
       <c r="R9" s="3">
         <v>300</v>
       </c>
       <c r="S9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T9" s="3">
         <v>300</v>
       </c>
       <c r="U9" s="3">
+        <v>300</v>
+      </c>
+      <c r="V9" s="3">
         <v>400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>300</v>
       </c>
-      <c r="W9" s="3">
-        <v>200</v>
-      </c>
       <c r="X9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y9" s="3">
         <v>300</v>
       </c>
       <c r="Z9" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AA9" s="3">
         <v>300</v>
@@ -1001,7 +1022,7 @@
         <v>300</v>
       </c>
       <c r="AC9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AD9" s="3">
         <v>300</v>
@@ -1013,135 +1034,153 @@
         <v>300</v>
       </c>
       <c r="AG9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AK9" s="3">
         <v>400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AL9" s="3">
         <v>400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AM9" s="3">
         <v>600</v>
       </c>
-      <c r="AK9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL9" s="3" t="s">
+      <c r="AN9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>500</v>
+      </c>
+      <c r="G10" s="3">
         <v>-100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>600</v>
       </c>
       <c r="H10" s="3">
         <v>-400</v>
       </c>
       <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>600</v>
+      </c>
+      <c r="K10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L10" s="3">
         <v>-300</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>4600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>-400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>1500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>1900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>2200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>8600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>1800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>1600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>1300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>1500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AE10" s="3">
         <v>500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <v>400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AG10" s="3">
         <v>1200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AH10" s="3">
         <v>1500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AI10" s="3">
         <v>600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AJ10" s="3">
         <v>400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AK10" s="3">
         <v>1300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AL10" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AM10" s="3">
         <v>600</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL10" s="3" t="s">
+      <c r="AN10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1219,11 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1332,17 @@
       <c r="AL12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1451,17 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1421,31 +1481,31 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1453,18 +1513,18 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1474,14 +1534,14 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1504,14 +1564,23 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1546,13 +1615,13 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1614,14 +1683,23 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL15" s="3" t="s">
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1735,249 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1700</v>
       </c>
       <c r="J17" s="3">
         <v>2500</v>
       </c>
       <c r="K17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>2400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>1400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1900</v>
       </c>
       <c r="AB17" s="3">
         <v>1400</v>
       </c>
       <c r="AC17" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="AD17" s="3">
         <v>1900</v>
       </c>
       <c r="AE17" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="AF17" s="3">
         <v>1400</v>
       </c>
       <c r="AG17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>1500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AK17" s="3">
         <v>1900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AL17" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AM17" s="3">
         <v>1800</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL17" s="3" t="s">
+      <c r="AN17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>100</v>
       </c>
       <c r="H18" s="3">
         <v>-900</v>
       </c>
       <c r="I18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-700</v>
       </c>
       <c r="R18" s="3">
         <v>-100</v>
       </c>
       <c r="S18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V18" s="3">
         <v>200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>7600</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
         <v>-100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AE18" s="3">
         <v>-600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AI18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AJ18" s="3">
         <v>-700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AK18" s="3">
         <v>-200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AL18" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AM18" s="3">
         <v>-600</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL18" s="3" t="s">
+      <c r="AN18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,13 +2016,16 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1934,8 +2036,8 @@
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
@@ -1943,8 +2045,8 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
@@ -1952,50 +2054,50 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>-100</v>
@@ -2004,16 +2106,16 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
       <c r="AH20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3">
         <v>100</v>
@@ -2021,124 +2123,142 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL20" s="3" t="s">
+      <c r="AK20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>200</v>
       </c>
       <c r="H21" s="3">
         <v>-800</v>
       </c>
       <c r="I21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="N21" s="3">
         <v>100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="T21" s="3">
         <v>-600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
         <v>400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="X21" s="3">
         <v>7700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AB21" s="3">
         <v>-600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AC21" s="3">
         <v>-300</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AF21" s="3">
         <v>-600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AG21" s="3">
         <v>-200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AH21" s="3">
         <v>-100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AI21" s="3">
         <v>-300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AJ21" s="3">
         <v>-500</v>
       </c>
-      <c r="AH21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="3">
         <v>-400</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2154,8 +2274,8 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -2163,8 +2283,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2230,227 +2350,245 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL22" s="3" t="s">
+      <c r="AK22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>100</v>
+      </c>
+      <c r="F23" s="3">
+        <v>200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>4200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>7600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AE23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AF23" s="3">
         <v>-700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-800</v>
       </c>
       <c r="AH23" s="3">
         <v>-300</v>
       </c>
       <c r="AI23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AM23" s="3">
         <v>-700</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL23" s="3" t="s">
+      <c r="AN23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO23" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>-200</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>1100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
       </c>
       <c r="P24" s="3">
         <v>-200</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="X24" s="3">
         <v>1900</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-200</v>
       </c>
       <c r="Y24" s="3">
         <v>-100</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AG24" s="3">
         <v>100</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>-200</v>
       </c>
       <c r="AH24" s="3">
         <v>-100</v>
@@ -2461,14 +2599,23 @@
       <c r="AJ24" s="3">
         <v>-200</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL24" s="3" t="s">
+      <c r="AK24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AN24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2724,255 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>3100</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-100</v>
       </c>
       <c r="P26" s="3">
         <v>-500</v>
       </c>
       <c r="Q26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>5600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AB26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AC26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AF26" s="3">
         <v>-600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AG26" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>-600</v>
       </c>
       <c r="AH26" s="3">
         <v>-200</v>
       </c>
       <c r="AI26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AM26" s="3">
         <v>-400</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL26" s="3" t="s">
+      <c r="AN26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO26" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>3100</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-100</v>
       </c>
       <c r="P27" s="3">
         <v>-500</v>
       </c>
       <c r="Q27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T27" s="3">
         <v>-600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>5600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AB27" s="3">
         <v>-600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AC27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AE27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AF27" s="3">
         <v>-600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AG27" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-600</v>
       </c>
       <c r="AH27" s="3">
         <v>-200</v>
       </c>
       <c r="AI27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AM27" s="3">
         <v>-400</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL27" s="3" t="s">
+      <c r="AN27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO27" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +3081,17 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2960,65 +3143,74 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>300</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-200</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3319,17 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,13 +3438,22 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -3254,8 +3464,8 @@
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
@@ -3263,8 +3473,8 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
@@ -3272,50 +3482,50 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>100</v>
@@ -3324,16 +3534,16 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
       <c r="AH32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3">
         <v>-100</v>
@@ -3341,124 +3551,142 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL32" s="3" t="s">
+      <c r="AK32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>3100</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-100</v>
       </c>
       <c r="P33" s="3">
         <v>-500</v>
       </c>
       <c r="Q33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T33" s="3">
         <v>-600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>5600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AE33" s="3">
         <v>300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AF33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AG33" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-800</v>
       </c>
       <c r="AH33" s="3">
         <v>-200</v>
       </c>
       <c r="AI33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AM33" s="3">
         <v>-400</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL33" s="3" t="s">
+      <c r="AN33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO33" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3795,260 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>3100</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-100</v>
       </c>
       <c r="P35" s="3">
         <v>-500</v>
       </c>
       <c r="Q35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T35" s="3">
         <v>-600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>5600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AE35" s="3">
         <v>300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AF35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AG35" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-800</v>
       </c>
       <c r="AH35" s="3">
         <v>-200</v>
       </c>
       <c r="AI35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AM35" s="3">
         <v>-400</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL35" s="3" t="s">
+      <c r="AN35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO35" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45869</v>
+      </c>
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +4087,11 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,160 +4130,172 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G41" s="3">
         <v>8700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>8800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>9700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>10000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>10400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>9500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>9300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>8500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>8100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>4900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>7600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>8000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>9700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>10400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>11000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>11200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>11800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>4100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>3600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AA41" s="3">
         <v>3200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AB41" s="3">
         <v>2500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AC41" s="3">
         <v>3200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AD41" s="3">
         <v>5700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AE41" s="3">
         <v>5300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AF41" s="3">
         <v>2100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AG41" s="3">
         <v>2600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AH41" s="3">
         <v>2000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AI41" s="3">
         <v>1900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AJ41" s="3">
         <v>2200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AK41" s="3">
         <v>3100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AL41" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AM41" s="3">
         <v>2400</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL41" s="3" t="s">
+      <c r="AN41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F42" s="3">
         <v>2800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H42" s="3">
         <v>2300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>2300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
         <v>1700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>2500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>3000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>4300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>5000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>3800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4086,64 +4356,73 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
-      <c r="AK42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL42" s="3" t="s">
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO42" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
       </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
       </c>
       <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
         <v>200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
         <v>100</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R43" s="3">
         <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
@@ -4155,55 +4434,64 @@
         <v>100</v>
       </c>
       <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
       <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AE43" s="3">
         <v>500</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
         <v>200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AI43" s="3">
         <v>200</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3">
         <v>100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AM43" s="3">
         <v>300</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL43" s="3" t="s">
+      <c r="AN43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO43" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4237,14 +4525,14 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4306,85 +4594,94 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
-      <c r="AK44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL44" s="3" t="s">
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO44" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>300</v>
       </c>
       <c r="R45" s="3">
         <v>500</v>
       </c>
       <c r="S45" s="3">
+        <v>500</v>
+      </c>
+      <c r="T45" s="3">
+        <v>300</v>
+      </c>
+      <c r="U45" s="3">
+        <v>500</v>
+      </c>
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>300</v>
-      </c>
-      <c r="V45" s="3">
-        <v>500</v>
-      </c>
-      <c r="W45" s="3">
-        <v>400</v>
       </c>
       <c r="X45" s="3">
         <v>300</v>
       </c>
       <c r="Y45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="Z45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA45" s="3">
         <v>300</v>
@@ -4393,79 +4690,88 @@
         <v>300</v>
       </c>
       <c r="AC45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD45" s="3">
         <v>300</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>500</v>
       </c>
       <c r="AE45" s="3">
         <v>300</v>
       </c>
       <c r="AF45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI45" s="3">
         <v>400</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>300</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>400</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>300</v>
       </c>
       <c r="AJ45" s="3">
         <v>300</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL45" s="3" t="s">
+      <c r="AK45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F46" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G46" s="3">
         <v>12200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>11700</v>
-      </c>
-      <c r="F46" s="3">
-        <v>12800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>12800</v>
       </c>
       <c r="I46" s="3">
         <v>12800</v>
       </c>
       <c r="J46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K46" s="3">
+        <v>12800</v>
+      </c>
+      <c r="L46" s="3">
+        <v>12800</v>
+      </c>
+      <c r="M46" s="3">
         <v>12900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>13700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>14000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>9300</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4526,14 +4832,23 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL46" s="3" t="s">
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO46" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4567,136 +4882,145 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3">
         <v>3700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="R47" s="3">
         <v>2200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="S47" s="3">
         <v>2200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="T47" s="3">
         <v>900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="U47" s="3">
         <v>1000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="V47" s="3">
         <v>1000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="W47" s="3">
         <v>1200</v>
-      </c>
-      <c r="U47" s="3">
-        <v>1300</v>
-      </c>
-      <c r="V47" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W47" s="3">
-        <v>1300</v>
       </c>
       <c r="X47" s="3">
         <v>1300</v>
       </c>
       <c r="Y47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB47" s="3">
         <v>2400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AC47" s="3">
         <v>2400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AD47" s="3">
         <v>2400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AE47" s="3">
         <v>2600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AF47" s="3">
         <v>2600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AG47" s="3">
         <v>2600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AH47" s="3">
         <v>3800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AI47" s="3">
         <v>4000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AJ47" s="3">
         <v>4000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AK47" s="3">
         <v>4400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AL47" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AM47" s="3">
         <v>5500</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL47" s="3" t="s">
+      <c r="AN47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO47" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="G48" s="3">
         <v>8900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>9100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>9100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>9100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>9200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>9300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>9200</v>
       </c>
       <c r="L48" s="3">
         <v>9200</v>
       </c>
       <c r="M48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="O48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="P48" s="3">
         <v>9100</v>
-      </c>
-      <c r="N48" s="3">
-        <v>10500</v>
-      </c>
-      <c r="O48" s="3">
-        <v>10700</v>
-      </c>
-      <c r="P48" s="3">
-        <v>10600</v>
       </c>
       <c r="Q48" s="3">
         <v>10500</v>
       </c>
       <c r="R48" s="3">
-        <v>10500</v>
+        <v>10700</v>
       </c>
       <c r="S48" s="3">
         <v>10600</v>
       </c>
       <c r="T48" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="U48" s="3">
         <v>10500</v>
@@ -4708,52 +5032,61 @@
         <v>10600</v>
       </c>
       <c r="X48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>10700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AB48" s="3">
         <v>10700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AC48" s="3">
         <v>10700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AD48" s="3">
         <v>10900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AE48" s="3">
         <v>10900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AF48" s="3">
         <v>10900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AG48" s="3">
         <v>20400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AH48" s="3">
         <v>20600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AI48" s="3">
         <v>16000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AJ48" s="3">
         <v>20800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AK48" s="3">
         <v>20900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AL48" s="3">
         <v>21100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AM48" s="3">
         <v>21300</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL48" s="3" t="s">
+      <c r="AN48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4856,14 +5189,23 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL49" s="3" t="s">
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5314,17 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5433,17 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5103,7 +5463,7 @@
         <v>1500</v>
       </c>
       <c r="I52" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="J52" s="3">
         <v>1500</v>
@@ -5112,29 +5472,29 @@
         <v>1500</v>
       </c>
       <c r="L52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="M52" s="3">
         <v>1500</v>
       </c>
       <c r="N52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
@@ -5142,58 +5502,67 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Z52" s="3">
         <v>1500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AA52" s="3">
         <v>2100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AB52" s="3">
         <v>1900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AC52" s="3">
         <v>1700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AD52" s="3">
         <v>1600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AE52" s="3">
         <v>1600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AF52" s="3">
         <v>10400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AG52" s="3">
         <v>900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AH52" s="3">
         <v>1200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AI52" s="3">
         <v>5800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AJ52" s="3">
         <v>1000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AK52" s="3">
         <v>1000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AL52" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AM52" s="3">
         <v>1100</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL52" s="3" t="s">
+      <c r="AN52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5671,136 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22300</v>
+      </c>
+      <c r="F54" s="3">
+        <v>22700</v>
+      </c>
+      <c r="G54" s="3">
         <v>22600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>22200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>23400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>23600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>23400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>23300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>23700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>24400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>24700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>20100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>20700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>21400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>21600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>21600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>22500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>23200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>23700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>24000</v>
-      </c>
-      <c r="V54" s="3">
-        <v>17900</v>
-      </c>
-      <c r="W54" s="3">
-        <v>18100</v>
-      </c>
-      <c r="X54" s="3">
-        <v>17600</v>
       </c>
       <c r="Y54" s="3">
         <v>17900</v>
       </c>
       <c r="Z54" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>17600</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>17900</v>
+      </c>
+      <c r="AC54" s="3">
         <v>18600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AD54" s="3">
         <v>21000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AE54" s="3">
         <v>21200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AF54" s="3">
         <v>26400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AG54" s="3">
         <v>27000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AH54" s="3">
         <v>28100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AI54" s="3">
         <v>28300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AJ54" s="3">
         <v>28300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AK54" s="3">
         <v>30000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AL54" s="3">
         <v>30700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AM54" s="3">
         <v>30900</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL54" s="3" t="s">
+      <c r="AN54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5839,11 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,118 +5882,130 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>500</v>
+      </c>
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>500</v>
       </c>
       <c r="I57" s="3">
         <v>300</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K57" s="3">
         <v>500</v>
       </c>
       <c r="L57" s="3">
+        <v>300</v>
+      </c>
+      <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
-        <v>400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>400</v>
-      </c>
       <c r="O57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P57" s="3">
         <v>400</v>
       </c>
       <c r="Q57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="R57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>200</v>
+      </c>
+      <c r="U57" s="3">
+        <v>300</v>
+      </c>
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
+        <v>400</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Y57" s="3">
         <v>300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>200</v>
       </c>
       <c r="AA57" s="3">
         <v>300</v>
       </c>
       <c r="AB57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
       </c>
       <c r="AD57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE57" s="3">
         <v>300</v>
       </c>
       <c r="AF57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG57" s="3">
         <v>200</v>
       </c>
       <c r="AH57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AI57" s="3">
         <v>300</v>
       </c>
       <c r="AJ57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL57" s="3">
         <v>300</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL57" s="3" t="s">
+      <c r="AM57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5659,23 +6061,23 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Y58" s="3">
         <v>500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Z58" s="3">
         <v>500</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
@@ -5686,13 +6088,13 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AG58" s="3">
         <v>300</v>
@@ -5701,30 +6103,39 @@
         <v>300</v>
       </c>
       <c r="AI58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AJ58" s="3">
         <v>300</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL58" s="3" t="s">
+      <c r="AK58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO58" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
@@ -5732,11 +6143,11 @@
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -5744,35 +6155,35 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>500</v>
-      </c>
-      <c r="S59" s="3">
-        <v>400</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
       </c>
       <c r="U59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="V59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
@@ -5781,91 +6192,100 @@
         <v>300</v>
       </c>
       <c r="Y59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AC59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AD59" s="3">
         <v>700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AE59" s="3">
         <v>3200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AF59" s="3">
         <v>2900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AG59" s="3">
         <v>3000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AH59" s="3">
         <v>3900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AI59" s="3">
         <v>3700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AJ59" s="3">
         <v>3600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AK59" s="3">
         <v>4400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AL59" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AM59" s="3">
         <v>4800</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL59" s="3" t="s">
+      <c r="AN59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E60" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="F60" s="3">
         <v>1000</v>
       </c>
       <c r="G60" s="3">
+        <v>800</v>
+      </c>
+      <c r="H60" s="3">
+        <v>500</v>
+      </c>
+      <c r="I60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -5926,14 +6346,23 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL60" s="3" t="s">
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO60" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6007,43 +6436,52 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AE61" s="3">
         <v>100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AF61" s="3">
         <v>100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AG61" s="3">
         <v>6000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AH61" s="3">
         <v>6100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AI61" s="3">
         <v>3300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AJ61" s="3">
         <v>6300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AK61" s="3">
         <v>6400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AL61" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AM61" s="3">
         <v>6500</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6077,72 +6515,72 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="S62" s="3">
         <v>400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="T62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="U62" s="3">
         <v>800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="V62" s="3">
         <v>1500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="W62" s="3">
         <v>2000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="X62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Y62" s="3">
         <v>1400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Z62" s="3">
         <v>1900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AA62" s="3">
         <v>1800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AB62" s="3">
         <v>1700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AC62" s="3">
         <v>1700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AD62" s="3">
         <v>2700</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
         <v>6200</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI62" s="3">
         <v>3100</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
@@ -6152,8 +6590,17 @@
       <c r="AL62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6709,17 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6828,17 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6947,136 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="E66" s="3">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="F66" s="3">
         <v>1800</v>
       </c>
       <c r="G66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J66" s="3">
         <v>2300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1800</v>
       </c>
       <c r="K66" s="3">
         <v>2300</v>
       </c>
       <c r="L66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N66" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O66" s="3">
         <v>2700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>1200</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1900</v>
       </c>
       <c r="Q66" s="3">
         <v>1300</v>
       </c>
       <c r="R66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U66" s="3">
         <v>1800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>2700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>3400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>3400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>2900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>3500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AA66" s="3">
         <v>3000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AB66" s="3">
         <v>2500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AC66" s="3">
         <v>2700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AD66" s="3">
         <v>4100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AE66" s="3">
         <v>4200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AF66" s="3">
         <v>9600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AG66" s="3">
         <v>9700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AH66" s="3">
         <v>10900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AI66" s="3">
         <v>11000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AJ66" s="3">
         <v>10600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AK66" s="3">
         <v>11500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AL66" s="3">
         <v>12300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AM66" s="3">
         <v>12400</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL66" s="3" t="s">
+      <c r="AN66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +7115,11 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +7228,17 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7347,17 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6956,14 +7460,23 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
-      <c r="AK70" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL70" s="3" t="s">
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO70" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7585,136 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G72" s="3">
         <v>2800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>3100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>3700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>3700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>3500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>4000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>4300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>4600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>4500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>1400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>1900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>2200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>2300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>2800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>3300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>3500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="W72" s="3">
         <v>3300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>3500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>-2100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>-1900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AA72" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AB72" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AC72" s="3">
         <v>-700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AD72" s="3">
         <v>-300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AE72" s="3">
         <v>-200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AF72" s="3">
         <v>-500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AG72" s="3">
         <v>100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AH72" s="3">
         <v>400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AI72" s="3">
         <v>600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AJ72" s="3">
         <v>1000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AK72" s="3">
         <v>1500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AL72" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AM72" s="3">
         <v>1900</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL72" s="3" t="s">
+      <c r="AN72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7823,17 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7942,17 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +8061,136 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F76" s="3">
+        <v>20900</v>
+      </c>
+      <c r="G76" s="3">
         <v>20700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>21000</v>
-      </c>
-      <c r="F76" s="3">
-        <v>21600</v>
-      </c>
-      <c r="G76" s="3">
-        <v>21300</v>
-      </c>
-      <c r="H76" s="3">
-        <v>21100</v>
       </c>
       <c r="I76" s="3">
         <v>21600</v>
       </c>
       <c r="J76" s="3">
+        <v>21300</v>
+      </c>
+      <c r="K76" s="3">
+        <v>21100</v>
+      </c>
+      <c r="L76" s="3">
+        <v>21600</v>
+      </c>
+      <c r="M76" s="3">
         <v>21900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>22100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>22000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>18900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>19400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>19700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>19800</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>20200</v>
-      </c>
-      <c r="R76" s="3">
-        <v>20800</v>
-      </c>
-      <c r="S76" s="3">
-        <v>20500</v>
       </c>
       <c r="T76" s="3">
         <v>20200</v>
       </c>
       <c r="U76" s="3">
+        <v>20800</v>
+      </c>
+      <c r="V76" s="3">
+        <v>20500</v>
+      </c>
+      <c r="W76" s="3">
+        <v>20200</v>
+      </c>
+      <c r="X76" s="3">
         <v>20600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>15000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>14600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AA76" s="3">
         <v>14600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AB76" s="3">
         <v>15400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AC76" s="3">
         <v>15900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AD76" s="3">
         <v>16900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AE76" s="3">
         <v>17100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AF76" s="3">
         <v>16700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AG76" s="3">
         <v>17300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AH76" s="3">
         <v>17200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AI76" s="3">
         <v>17300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AJ76" s="3">
         <v>17700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AK76" s="3">
         <v>18500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AL76" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AM76" s="3">
         <v>18500</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL76" s="3" t="s">
+      <c r="AN76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +8299,260 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45869</v>
+      </c>
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
+        <v>200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>3100</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-100</v>
       </c>
       <c r="P81" s="3">
         <v>-500</v>
       </c>
       <c r="Q81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T81" s="3">
         <v>-600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>5600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AE81" s="3">
         <v>300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AF81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AG81" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-800</v>
       </c>
       <c r="AH81" s="3">
         <v>-200</v>
       </c>
       <c r="AI81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AM81" s="3">
         <v>-400</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL81" s="3" t="s">
+      <c r="AN81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO81" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8591,11 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8078,13 +8675,13 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
         <v>200</v>
@@ -8101,14 +8698,23 @@
       <c r="AJ83" s="3">
         <v>200</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL83" s="3" t="s">
+      <c r="AK83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AN83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8823,17 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8942,17 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +9061,17 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +9180,17 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +9299,136 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>200</v>
+      </c>
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>200</v>
-      </c>
-      <c r="H89" s="3">
-        <v>200</v>
       </c>
       <c r="I89" s="3">
         <v>-200</v>
       </c>
       <c r="J89" s="3">
+        <v>200</v>
+      </c>
+      <c r="K89" s="3">
+        <v>200</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="X89" s="3">
         <v>7700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Y89" s="3">
         <v>500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AC89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AD89" s="3">
         <v>400</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AJ89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AK89" s="3">
         <v>-300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AL89" s="3">
         <v>200</v>
       </c>
-      <c r="AJ89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,28 +9467,31 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-500</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -8837,40 +9500,40 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -8882,43 +9545,52 @@
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-200</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL91" s="3" t="s">
+      <c r="AN91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9699,17 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9818,136 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-200</v>
       </c>
       <c r="G94" s="3">
         <v>-500</v>
       </c>
       <c r="H94" s="3">
-        <v>700</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
-        <v>400</v>
+        <v>-200</v>
       </c>
       <c r="J94" s="3">
-        <v>1200</v>
+        <v>-500</v>
       </c>
       <c r="K94" s="3">
         <v>700</v>
       </c>
       <c r="L94" s="3">
+        <v>400</v>
+      </c>
+      <c r="M94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N94" s="3">
+        <v>700</v>
+      </c>
+      <c r="O94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="S94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="V94" s="3">
         <v>200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>900</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AD94" s="3">
         <v>100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AE94" s="3">
         <v>3200</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>1100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AH94" s="3">
         <v>200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AJ94" s="3">
         <v>300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AK94" s="3">
         <v>600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AL94" s="3">
         <v>400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AM94" s="3">
         <v>600</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL94" s="3" t="s">
+      <c r="AN94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9986,11 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9322,14 +10024,14 @@
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9397,8 +10099,17 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +10218,17 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +10337,17 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,13 +10456,22 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -9744,32 +10482,32 @@
       <c r="G100" s="3">
         <v>0</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -9781,40 +10519,40 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="3">
         <v>-100</v>
       </c>
       <c r="AE100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF100" s="3">
         <v>-100</v>
@@ -9829,16 +10567,25 @@
         <v>-100</v>
       </c>
       <c r="AJ100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM100" s="3">
         <v>100</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AN100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9872,14 +10619,14 @@
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9941,120 +10688,138 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL101" s="3" t="s">
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>3300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-2000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="S102" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="W102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="X102" s="3">
         <v>7600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Y102" s="3">
         <v>500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AA102" s="3">
         <v>700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AB102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AC102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AE102" s="3">
         <v>3200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AF102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AI102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AJ102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AK102" s="3">
         <v>300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AL102" s="3">
         <v>400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AM102" s="3">
         <v>700</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AN102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>BRRE</t>
   </si>
@@ -9313,8 +9313,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4</v>
+      <c r="D89" s="3">
+        <v>-700</v>
       </c>
       <c r="E89" s="3">
         <v>-100</v>
@@ -9475,8 +9475,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-300</v>
@@ -9832,8 +9832,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>300</v>
       </c>
       <c r="E94" s="3">
         <v>-600</v>
@@ -10470,8 +10470,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>0</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -10709,7 +10709,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E102" s="3">
         <v>-700</v>
